--- a/research/traditional_assets/database/data/pakistan/pakistan_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_retail_automotive.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kase_modam" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04615000000000001</v>
+        <v>0.003500000000000003</v>
       </c>
       <c r="E2">
-        <v>0.584</v>
+        <v>0.597</v>
       </c>
       <c r="G2">
-        <v>-0.09923407835860401</v>
+        <v>-0.01137809135013608</v>
       </c>
       <c r="H2">
-        <v>-0.09923407835860401</v>
+        <v>-0.01137809135013608</v>
       </c>
       <c r="I2">
-        <v>-0.1133809213349159</v>
+        <v>-0.06580212400899303</v>
       </c>
       <c r="J2">
-        <v>-0.1096599258470905</v>
+        <v>-0.05903741967161991</v>
       </c>
       <c r="K2">
-        <v>-157.457</v>
+        <v>-55.226</v>
       </c>
       <c r="L2">
-        <v>-0.2193519896131106</v>
+        <v>-0.2042139983433914</v>
       </c>
       <c r="M2">
-        <v>0.0398</v>
+        <v>0.027</v>
       </c>
       <c r="N2">
-        <v>0.001103012498960729</v>
+        <v>0.001016949152542373</v>
       </c>
       <c r="O2">
-        <v>-0.0002527674222168592</v>
+        <v>-0.0004889001557237533</v>
       </c>
       <c r="P2">
-        <v>0.0398</v>
+        <v>0.027</v>
       </c>
       <c r="Q2">
-        <v>0.001103012498960729</v>
+        <v>0.001016949152542373</v>
       </c>
       <c r="R2">
-        <v>-0.0002527674222168592</v>
+        <v>-0.0004889001557237533</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>20.6</v>
+        <v>6.754</v>
       </c>
       <c r="V2">
-        <v>0.5709059667987695</v>
+        <v>0.2543879472693032</v>
       </c>
       <c r="W2">
-        <v>0.6017634514435695</v>
+        <v>0.210560068854042</v>
       </c>
       <c r="X2">
-        <v>0.4832589672766203</v>
+        <v>0.6549719870677924</v>
       </c>
       <c r="Y2">
-        <v>0.1185044841669491</v>
+        <v>-0.4444119182137504</v>
       </c>
       <c r="Z2">
-        <v>4.361998979120585</v>
+        <v>20.51836115326252</v>
       </c>
       <c r="AA2">
-        <v>-0.2429619691766005</v>
+        <v>-0.7034984518860883</v>
       </c>
       <c r="AB2">
-        <v>0.1155967664116429</v>
+        <v>0.186830614701781</v>
       </c>
       <c r="AC2">
-        <v>-0.3585587355882434</v>
+        <v>-0.8903290665878693</v>
       </c>
       <c r="AD2">
-        <v>402.2</v>
+        <v>246</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>402.2</v>
+        <v>246</v>
       </c>
       <c r="AG2">
-        <v>381.6</v>
+        <v>239.246</v>
       </c>
       <c r="AH2">
-        <v>0.9176719151780927</v>
+        <v>0.9025866813428728</v>
       </c>
       <c r="AI2">
-        <v>3.594923131927065</v>
+        <v>144.7058823529397</v>
       </c>
       <c r="AJ2">
-        <v>0.9136115187833835</v>
+        <v>0.9001113636021612</v>
       </c>
       <c r="AK2">
-        <v>4.180543382997372</v>
+        <v>-47.3379501385044</v>
       </c>
       <c r="AL2">
-        <v>49.7</v>
+        <v>32.412</v>
       </c>
       <c r="AM2">
-        <v>48.12</v>
+        <v>32.178</v>
       </c>
       <c r="AN2">
-        <v>-5.642140702812654</v>
+        <v>-21.21604139715394</v>
       </c>
       <c r="AO2">
-        <v>-1.637585513078471</v>
+        <v>-0.54902505244971</v>
       </c>
       <c r="AP2">
-        <v>-5.353159851301115</v>
+        <v>-20.63354894351013</v>
       </c>
       <c r="AQ2">
-        <v>-1.691354945968412</v>
+        <v>-0.5530175896575301</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.176</v>
+        <v>0.174</v>
       </c>
       <c r="E3">
-        <v>0.584</v>
+        <v>0.597</v>
       </c>
       <c r="G3">
-        <v>0.5234375</v>
+        <v>0.231203007518797</v>
       </c>
       <c r="H3">
-        <v>0.5234375</v>
+        <v>0.231203007518797</v>
       </c>
       <c r="I3">
-        <v>0.09375</v>
+        <v>0.5733082706766917</v>
       </c>
       <c r="J3">
-        <v>0.0875965250965251</v>
+        <v>0.4554318038085868</v>
       </c>
       <c r="K3">
-        <v>0.243</v>
+        <v>0.374</v>
       </c>
       <c r="L3">
-        <v>1.8984375</v>
+        <v>0.7030075187969924</v>
       </c>
       <c r="M3">
-        <v>0.0368</v>
+        <v>0.027</v>
       </c>
       <c r="N3">
-        <v>0.04167610419026047</v>
+        <v>0.01542857142857143</v>
       </c>
       <c r="O3">
-        <v>0.151440329218107</v>
+        <v>0.07219251336898395</v>
       </c>
       <c r="P3">
-        <v>0.0368</v>
+        <v>0.027</v>
       </c>
       <c r="Q3">
-        <v>0.04167610419026047</v>
+        <v>0.01542857142857143</v>
       </c>
       <c r="R3">
-        <v>0.151440329218107</v>
+        <v>0.07219251336898395</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +772,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.01371428571428572</v>
       </c>
       <c r="W3">
-        <v>0.16875</v>
+        <v>0.2367088607594937</v>
       </c>
       <c r="X3">
-        <v>0.1076896339954098</v>
+        <v>0.1750799008229845</v>
       </c>
       <c r="Y3">
-        <v>0.06106036600459018</v>
+        <v>0.06162895993650916</v>
       </c>
       <c r="Z3">
-        <v>0.1327800829875519</v>
+        <v>0.3367088607594937</v>
       </c>
       <c r="AA3">
-        <v>0.01163107387173777</v>
+        <v>0.1533479238140305</v>
       </c>
       <c r="AB3">
-        <v>0.1076896339954098</v>
+        <v>0.1750799008229845</v>
       </c>
       <c r="AC3">
-        <v>-0.09605856012367206</v>
+        <v>-0.02173197700895399</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,22 +817,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.01390498261877173</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-0.004922067268252666</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>25.41666666666666</v>
+      </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.07868852459016394</v>
+      </c>
+      <c r="AQ3">
+        <v>25.41666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -850,118 +858,8827 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0837</v>
+        <v>-0.167</v>
       </c>
       <c r="G4">
-        <v>-0.09934513027727462</v>
+        <v>-0.01185624305298259</v>
       </c>
       <c r="H4">
-        <v>-0.09934513027727462</v>
+        <v>-0.01185624305298259</v>
       </c>
       <c r="I4">
-        <v>-0.1134178626166922</v>
+        <v>-0.06706187476843277</v>
       </c>
       <c r="J4">
-        <v>-0.1134178626166922</v>
+        <v>-0.06706187476843277</v>
       </c>
       <c r="K4">
-        <v>-157.7</v>
+        <v>-55.6</v>
       </c>
       <c r="L4">
-        <v>-0.2197296920718963</v>
+        <v>-0.2060022230455724</v>
       </c>
       <c r="M4">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>8.522727272727272e-05</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-1.902346227013317e-05</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>8.522727272727272e-05</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-1.902346227013317e-05</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="U4">
+        <v>6.73</v>
+      </c>
+      <c r="V4">
+        <v>0.2713709677419355</v>
+      </c>
+      <c r="W4">
+        <v>0.1844112769485904</v>
+      </c>
+      <c r="X4">
+        <v>1.1348640733126</v>
+      </c>
+      <c r="Y4">
+        <v>-0.9504527963640099</v>
+      </c>
+      <c r="Z4">
+        <v>23.26724137931035</v>
+      </c>
+      <c r="AA4">
+        <v>-1.560344827586207</v>
+      </c>
+      <c r="AB4">
+        <v>0.1985813285805775</v>
+      </c>
+      <c r="AC4">
+        <v>-1.758926156166785</v>
+      </c>
+      <c r="AD4">
+        <v>246</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>246</v>
+      </c>
+      <c r="AG4">
+        <v>239.27</v>
+      </c>
+      <c r="AH4">
+        <v>0.9084194977843426</v>
+      </c>
+      <c r="AI4">
+        <v>-76.87500000000027</v>
+      </c>
+      <c r="AJ4">
+        <v>0.9060855076305526</v>
+      </c>
+      <c r="AK4">
+        <v>-24.09566968781476</v>
+      </c>
+      <c r="AL4">
+        <v>32.4</v>
+      </c>
+      <c r="AM4">
+        <v>32.166</v>
+      </c>
+      <c r="AN4">
+        <v>-20.67226890756302</v>
+      </c>
+      <c r="AO4">
+        <v>-0.558641975308642</v>
+      </c>
+      <c r="AP4">
+        <v>-20.10672268907563</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.5627059628178823</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Modaraba Al-Mali (KASE:MODAM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KASE:MODAM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Automotive)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.7</v>
+      </c>
+      <c r="G2">
+        <v>1.75</v>
+      </c>
+      <c r="H2">
+        <v>0.961137455488991</v>
+      </c>
+      <c r="I2">
+        <v>1.726</v>
+      </c>
+      <c r="J2">
+        <v>2.16213745548899</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1.225</v>
+      </c>
+      <c r="M2">
+        <v>0.175079900822984</v>
+      </c>
+      <c r="N2">
+        <v>0.147590080955919</v>
+      </c>
+      <c r="O2">
+        <v>0.106889848623853</v>
+      </c>
+      <c r="P2">
+        <v>0.03905</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.175079900822984</v>
+      </c>
+      <c r="T2">
+        <v>0.400850269853062</v>
+      </c>
+      <c r="U2">
+        <v>0.722717571455129</v>
+      </c>
+      <c r="V2">
+        <v>1.92001968149913</v>
+      </c>
+      <c r="W2">
+        <v>4.526901669758812</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1.75</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1505490825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.29</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.305</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.012</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0.024</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1750799008229845</v>
+      </c>
+      <c r="C2">
+        <v>1.75</v>
+      </c>
+      <c r="D2">
+        <v>1.726</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.024</v>
+      </c>
+      <c r="H2">
+        <v>1.75</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.305</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0.305</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.305</v>
+      </c>
+      <c r="O2">
+        <v>0.08845000000000001</v>
+      </c>
+      <c r="P2">
+        <v>0.21655</v>
+      </c>
+      <c r="Q2">
+        <v>0.21655</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1750799008229845</v>
+      </c>
+      <c r="T2">
+        <v>0.7227175714551295</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.29</v>
+      </c>
+      <c r="W2">
+        <v>0.032447</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1746211591105978</v>
+      </c>
+      <c r="C3">
+        <v>1.738329638038464</v>
+      </c>
+      <c r="D3">
+        <v>1.731829638038464</v>
+      </c>
+      <c r="E3">
+        <v>0.0175</v>
+      </c>
+      <c r="F3">
+        <v>0.0175</v>
+      </c>
+      <c r="G3">
+        <v>0.024</v>
+      </c>
+      <c r="H3">
+        <v>1.75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.305</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0.305</v>
+      </c>
+      <c r="M3">
+        <v>0.0007997500000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.30420025</v>
+      </c>
+      <c r="O3">
+        <v>0.08821807250000001</v>
+      </c>
+      <c r="P3">
+        <v>0.2159821775</v>
+      </c>
+      <c r="Q3">
+        <v>0.2159821775</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1760572617278766</v>
+      </c>
+      <c r="T3">
+        <v>0.727900697472636</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.29</v>
+      </c>
+      <c r="W3">
+        <v>0.032447</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>381.3691778680837</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1741624173982112</v>
+      </c>
+      <c r="C4">
+        <v>1.726698789232614</v>
+      </c>
+      <c r="D4">
+        <v>1.737698789232614</v>
+      </c>
+      <c r="E4">
+        <v>0.035</v>
+      </c>
+      <c r="F4">
+        <v>0.035</v>
+      </c>
+      <c r="G4">
+        <v>0.024</v>
+      </c>
+      <c r="H4">
+        <v>1.75</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.305</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0.305</v>
+      </c>
+      <c r="M4">
+        <v>0.0015995</v>
+      </c>
+      <c r="N4">
+        <v>0.3034005</v>
+      </c>
+      <c r="O4">
+        <v>0.08798614500000002</v>
+      </c>
+      <c r="P4">
+        <v>0.215414355</v>
+      </c>
+      <c r="Q4">
+        <v>0.215414355</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1770545687736849</v>
+      </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.7331896015721324</v>
       </c>
       <c r="U4">
-        <v>20.6</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
-        <v>0.5852272727272727</v>
+        <v>0.29</v>
       </c>
       <c r="W4">
-        <v>1.034776902887139</v>
-      </c>
-      <c r="X4">
-        <v>0.8588283005578308</v>
+        <v>0.032447</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y4">
-        <v>0.1759486023293082</v>
+        <v>190.6845889340419</v>
       </c>
       <c r="Z4">
-        <v>4.386919315403422</v>
-      </c>
-      <c r="AA4">
-        <v>-0.4975550122249389</v>
-      </c>
-      <c r="AB4">
-        <v>0.1235038988278759</v>
-      </c>
-      <c r="AC4">
-        <v>-0.6210589110528147</v>
-      </c>
-      <c r="AD4">
-        <v>402.2</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>402.2</v>
-      </c>
-      <c r="AG4">
-        <v>381.6</v>
-      </c>
-      <c r="AH4">
-        <v>0.9195244627343393</v>
-      </c>
-      <c r="AI4">
-        <v>3.646418857660924</v>
-      </c>
-      <c r="AJ4">
-        <v>0.9155470249520153</v>
-      </c>
-      <c r="AK4">
-        <v>4.254180602006689</v>
-      </c>
-      <c r="AL4">
-        <v>49.7</v>
-      </c>
-      <c r="AM4">
-        <v>48.12</v>
-      </c>
-      <c r="AN4">
-        <v>-5.640953716690042</v>
-      </c>
-      <c r="AO4">
-        <v>-1.637826961770624</v>
-      </c>
-      <c r="AP4">
-        <v>-5.35203366058906</v>
-      </c>
-      <c r="AQ4">
-        <v>-1.691604322527016</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1737036756858245</v>
+      </c>
+      <c r="C5">
+        <v>1.715107856677457</v>
+      </c>
+      <c r="D5">
+        <v>1.743607856677457</v>
+      </c>
+      <c r="E5">
+        <v>0.0525</v>
+      </c>
+      <c r="F5">
+        <v>0.0525</v>
+      </c>
+      <c r="G5">
+        <v>0.024</v>
+      </c>
+      <c r="H5">
+        <v>1.75</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.305</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0.305</v>
+      </c>
+      <c r="M5">
+        <v>0.00239925</v>
+      </c>
+      <c r="N5">
+        <v>0.30260075</v>
+      </c>
+      <c r="O5">
+        <v>0.08775421750000001</v>
+      </c>
+      <c r="P5">
+        <v>0.2148465325</v>
+      </c>
+      <c r="Q5">
+        <v>0.2148465325</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1780724388513655</v>
+      </c>
+      <c r="T5">
+        <v>0.7385875552406906</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.29</v>
+      </c>
+      <c r="W5">
+        <v>0.032447</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>127.1230592893612</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1732449339734379</v>
+      </c>
+      <c r="C6">
+        <v>1.703557248969628</v>
+      </c>
+      <c r="D6">
+        <v>1.749557248969628</v>
+      </c>
+      <c r="E6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0.024</v>
+      </c>
+      <c r="H6">
+        <v>1.75</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.305</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0.305</v>
+      </c>
+      <c r="M6">
+        <v>0.003199</v>
+      </c>
+      <c r="N6">
+        <v>0.301801</v>
+      </c>
+      <c r="O6">
+        <v>0.08752229</v>
+      </c>
+      <c r="P6">
+        <v>0.21427871</v>
+      </c>
+      <c r="Q6">
+        <v>0.21427871</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1791115145556645</v>
+      </c>
+      <c r="T6">
+        <v>0.7440979662773437</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.29</v>
+      </c>
+      <c r="W6">
+        <v>0.032447</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>95.34229446702092</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1727861922610512</v>
+      </c>
+      <c r="C7">
+        <v>1.692047380301572</v>
+      </c>
+      <c r="D7">
+        <v>1.755547380301572</v>
+      </c>
+      <c r="E7">
+        <v>0.08750000000000001</v>
+      </c>
+      <c r="F7">
+        <v>0.08750000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.024</v>
+      </c>
+      <c r="H7">
+        <v>1.75</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.305</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0.305</v>
+      </c>
+      <c r="M7">
+        <v>0.003998750000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.30100125</v>
+      </c>
+      <c r="O7">
+        <v>0.08729036250000001</v>
+      </c>
+      <c r="P7">
+        <v>0.2137108875</v>
+      </c>
+      <c r="Q7">
+        <v>0.2137108875</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1801724655379487</v>
+      </c>
+      <c r="T7">
+        <v>0.7497243859674001</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.29</v>
+      </c>
+      <c r="W7">
+        <v>0.032447</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>76.27383557361675</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1723274505486646</v>
+      </c>
+      <c r="C8">
+        <v>1.680578670557668</v>
+      </c>
+      <c r="D8">
+        <v>1.761578670557668</v>
+      </c>
+      <c r="E8">
+        <v>0.105</v>
+      </c>
+      <c r="F8">
+        <v>0.105</v>
+      </c>
+      <c r="G8">
+        <v>0.024</v>
+      </c>
+      <c r="H8">
+        <v>1.75</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.305</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0.305</v>
+      </c>
+      <c r="M8">
+        <v>0.004798500000000001</v>
+      </c>
+      <c r="N8">
+        <v>0.3002015</v>
+      </c>
+      <c r="O8">
+        <v>0.08705843500000002</v>
+      </c>
+      <c r="P8">
+        <v>0.213143065</v>
+      </c>
+      <c r="Q8">
+        <v>0.213143065</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1812559899453878</v>
+      </c>
+      <c r="T8">
+        <v>0.7554705167146917</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.29</v>
+      </c>
+      <c r="W8">
+        <v>0.032447</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>63.56152964468063</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1718687088362779</v>
+      </c>
+      <c r="C9">
+        <v>1.669151545412339</v>
+      </c>
+      <c r="D9">
+        <v>1.767651545412339</v>
+      </c>
+      <c r="E9">
+        <v>0.1225</v>
+      </c>
+      <c r="F9">
+        <v>0.1225</v>
+      </c>
+      <c r="G9">
+        <v>0.024</v>
+      </c>
+      <c r="H9">
+        <v>1.75</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.305</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0.305</v>
+      </c>
+      <c r="M9">
+        <v>0.005598250000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.29940175</v>
+      </c>
+      <c r="O9">
+        <v>0.0868265075</v>
+      </c>
+      <c r="P9">
+        <v>0.2125752425</v>
+      </c>
+      <c r="Q9">
+        <v>0.2125752425</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.182362815952987</v>
+      </c>
+      <c r="T9">
+        <v>0.7613402201662263</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.29</v>
+      </c>
+      <c r="W9">
+        <v>0.032447</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>54.48131112401195</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1714099671238913</v>
+      </c>
+      <c r="C10">
+        <v>1.657766436430205</v>
+      </c>
+      <c r="D10">
+        <v>1.773766436430205</v>
+      </c>
+      <c r="E10">
+        <v>0.14</v>
+      </c>
+      <c r="F10">
+        <v>0.14</v>
+      </c>
+      <c r="G10">
+        <v>0.024</v>
+      </c>
+      <c r="H10">
+        <v>1.75</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.305</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0.305</v>
+      </c>
+      <c r="M10">
+        <v>0.006398000000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.298602</v>
+      </c>
+      <c r="O10">
+        <v>0.08659458</v>
+      </c>
+      <c r="P10">
+        <v>0.21200742</v>
+      </c>
+      <c r="Q10">
+        <v>0.21200742</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.183493703395534</v>
+      </c>
+      <c r="T10">
+        <v>0.767337525866707</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.29</v>
+      </c>
+      <c r="W10">
+        <v>0.032447</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>47.67114723351046</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1709512254115046</v>
+      </c>
+      <c r="C11">
+        <v>1.646423781168313</v>
+      </c>
+      <c r="D11">
+        <v>1.779923781168313</v>
+      </c>
+      <c r="E11">
+        <v>0.1575</v>
+      </c>
+      <c r="F11">
+        <v>0.1575</v>
+      </c>
+      <c r="G11">
+        <v>0.024</v>
+      </c>
+      <c r="H11">
+        <v>1.75</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.305</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.305</v>
+      </c>
+      <c r="M11">
+        <v>0.007197750000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.29780225</v>
+      </c>
+      <c r="O11">
+        <v>0.08636265250000001</v>
+      </c>
+      <c r="P11">
+        <v>0.2114395975</v>
+      </c>
+      <c r="Q11">
+        <v>0.2114395975</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1846494455071479</v>
+      </c>
+      <c r="T11">
+        <v>0.773466640483682</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.29</v>
+      </c>
+      <c r="W11">
+        <v>0.032447</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>42.37435309645375</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1704924836991179</v>
+      </c>
+      <c r="C12">
+        <v>1.635124023280508</v>
+      </c>
+      <c r="D12">
+        <v>1.786124023280508</v>
+      </c>
+      <c r="E12">
+        <v>0.175</v>
+      </c>
+      <c r="F12">
+        <v>0.175</v>
+      </c>
+      <c r="G12">
+        <v>0.024</v>
+      </c>
+      <c r="H12">
+        <v>1.75</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.305</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0.305</v>
+      </c>
+      <c r="M12">
+        <v>0.007997500000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.2970025</v>
+      </c>
+      <c r="O12">
+        <v>0.08613072500000001</v>
+      </c>
+      <c r="P12">
+        <v>0.210871775</v>
+      </c>
+      <c r="Q12">
+        <v>0.210871775</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1858308707767977</v>
+      </c>
+      <c r="T12">
+        <v>0.7797319576477008</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.29</v>
+      </c>
+      <c r="W12">
+        <v>0.032447</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>38.13691778680838</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1700337419867313</v>
+      </c>
+      <c r="C13">
+        <v>1.623867612623997</v>
+      </c>
+      <c r="D13">
+        <v>1.792367612623998</v>
+      </c>
+      <c r="E13">
+        <v>0.1925</v>
+      </c>
+      <c r="F13">
+        <v>0.1925</v>
+      </c>
+      <c r="G13">
+        <v>0.024</v>
+      </c>
+      <c r="H13">
+        <v>1.75</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.305</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0.305</v>
+      </c>
+      <c r="M13">
+        <v>0.008797250000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.29620275</v>
+      </c>
+      <c r="O13">
+        <v>0.08589879750000001</v>
+      </c>
+      <c r="P13">
+        <v>0.2103039525</v>
+      </c>
+      <c r="Q13">
+        <v>0.2103039525</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1870388449289116</v>
+      </c>
+      <c r="T13">
+        <v>0.7861380684558549</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.29</v>
+      </c>
+      <c r="W13">
+        <v>0.032447</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>34.66992526073489</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1695750002743446</v>
+      </c>
+      <c r="C14">
+        <v>1.612655005368151</v>
+      </c>
+      <c r="D14">
+        <v>1.798655005368151</v>
+      </c>
+      <c r="E14">
+        <v>0.21</v>
+      </c>
+      <c r="F14">
+        <v>0.21</v>
+      </c>
+      <c r="G14">
+        <v>0.024</v>
+      </c>
+      <c r="H14">
+        <v>1.75</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.305</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0.305</v>
+      </c>
+      <c r="M14">
+        <v>0.009597000000000001</v>
+      </c>
+      <c r="N14">
+        <v>0.295403</v>
+      </c>
+      <c r="O14">
+        <v>0.08566687000000001</v>
+      </c>
+      <c r="P14">
+        <v>0.20973613</v>
+      </c>
+      <c r="Q14">
+        <v>0.20973613</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.188274273039028</v>
+      </c>
+      <c r="T14">
+        <v>0.7926897726914669</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.29</v>
+      </c>
+      <c r="W14">
+        <v>0.032447</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>31.78076482234031</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.169116258561958</v>
+      </c>
+      <c r="C15">
+        <v>1.601486664105599</v>
+      </c>
+      <c r="D15">
+        <v>1.804986664105599</v>
+      </c>
+      <c r="E15">
+        <v>0.2275</v>
+      </c>
+      <c r="F15">
+        <v>0.2275</v>
+      </c>
+      <c r="G15">
+        <v>0.024</v>
+      </c>
+      <c r="H15">
+        <v>1.75</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.305</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0.305</v>
+      </c>
+      <c r="M15">
+        <v>0.01039675</v>
+      </c>
+      <c r="N15">
+        <v>0.29460325</v>
+      </c>
+      <c r="O15">
+        <v>0.0854349425</v>
+      </c>
+      <c r="P15">
+        <v>0.2091683075</v>
+      </c>
+      <c r="Q15">
+        <v>0.2091683075</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.189538101795354</v>
+      </c>
+      <c r="T15">
+        <v>0.799392090817553</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.29</v>
+      </c>
+      <c r="W15">
+        <v>0.032447</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>29.33609060523721</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1686575168495713</v>
+      </c>
+      <c r="C16">
+        <v>1.590363057965695</v>
+      </c>
+      <c r="D16">
+        <v>1.811363057965695</v>
+      </c>
+      <c r="E16">
+        <v>0.245</v>
+      </c>
+      <c r="F16">
+        <v>0.245</v>
+      </c>
+      <c r="G16">
+        <v>0.024</v>
+      </c>
+      <c r="H16">
+        <v>1.75</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.305</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0.305</v>
+      </c>
+      <c r="M16">
+        <v>0.0111965</v>
+      </c>
+      <c r="N16">
+        <v>0.2938035</v>
+      </c>
+      <c r="O16">
+        <v>0.08520301500000001</v>
+      </c>
+      <c r="P16">
+        <v>0.208600485</v>
+      </c>
+      <c r="Q16">
+        <v>0.208600485</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1908313219181062</v>
+      </c>
+      <c r="T16">
+        <v>0.8062502768070363</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.29</v>
+      </c>
+      <c r="W16">
+        <v>0.032447</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>27.24065556200598</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1681987751371847</v>
+      </c>
+      <c r="C17">
+        <v>1.579284662730378</v>
+      </c>
+      <c r="D17">
+        <v>1.817784662730378</v>
+      </c>
+      <c r="E17">
+        <v>0.2625</v>
+      </c>
+      <c r="F17">
+        <v>0.2625</v>
+      </c>
+      <c r="G17">
+        <v>0.024</v>
+      </c>
+      <c r="H17">
+        <v>1.75</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.305</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0.305</v>
+      </c>
+      <c r="M17">
+        <v>0.01199625</v>
+      </c>
+      <c r="N17">
+        <v>0.29300375</v>
+      </c>
+      <c r="O17">
+        <v>0.08497108750000001</v>
+      </c>
+      <c r="P17">
+        <v>0.2080326625</v>
+      </c>
+      <c r="Q17">
+        <v>0.2080326625</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.192154970749629</v>
+      </c>
+      <c r="T17">
+        <v>0.8132698318786251</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.29</v>
+      </c>
+      <c r="W17">
+        <v>0.032447</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>25.42461185787225</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.167740033424798</v>
+      </c>
+      <c r="C18">
+        <v>1.56825196095252</v>
+      </c>
+      <c r="D18">
+        <v>1.82425196095252</v>
+      </c>
+      <c r="E18">
+        <v>0.28</v>
+      </c>
+      <c r="F18">
+        <v>0.28</v>
+      </c>
+      <c r="G18">
+        <v>0.024</v>
+      </c>
+      <c r="H18">
+        <v>1.75</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.305</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0.305</v>
+      </c>
+      <c r="M18">
+        <v>0.012796</v>
+      </c>
+      <c r="N18">
+        <v>0.292204</v>
+      </c>
+      <c r="O18">
+        <v>0.08473916000000002</v>
+      </c>
+      <c r="P18">
+        <v>0.20746484</v>
+      </c>
+      <c r="Q18">
+        <v>0.20746484</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1935101350295214</v>
+      </c>
+      <c r="T18">
+        <v>0.8204565192138231</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.29</v>
+      </c>
+      <c r="W18">
+        <v>0.032447</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>23.83557361675523</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1672812917124114</v>
+      </c>
+      <c r="C19">
+        <v>1.557265442076801</v>
+      </c>
+      <c r="D19">
+        <v>1.830765442076801</v>
+      </c>
+      <c r="E19">
+        <v>0.2975</v>
+      </c>
+      <c r="F19">
+        <v>0.2975</v>
+      </c>
+      <c r="G19">
+        <v>0.024</v>
+      </c>
+      <c r="H19">
+        <v>1.75</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.305</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0.305</v>
+      </c>
+      <c r="M19">
+        <v>0.01359575</v>
+      </c>
+      <c r="N19">
+        <v>0.29140425</v>
+      </c>
+      <c r="O19">
+        <v>0.0845072325</v>
+      </c>
+      <c r="P19">
+        <v>0.2068970175</v>
+      </c>
+      <c r="Q19">
+        <v>0.2068970175</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1948979538703751</v>
+      </c>
+      <c r="T19">
+        <v>0.8278163797378212</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.29</v>
+      </c>
+      <c r="W19">
+        <v>0.032447</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>22.43348105106374</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1668225500000247</v>
+      </c>
+      <c r="C20">
+        <v>1.546325602563188</v>
+      </c>
+      <c r="D20">
+        <v>1.837325602563188</v>
+      </c>
+      <c r="E20">
+        <v>0.315</v>
+      </c>
+      <c r="F20">
+        <v>0.315</v>
+      </c>
+      <c r="G20">
+        <v>0.024</v>
+      </c>
+      <c r="H20">
+        <v>1.75</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.305</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0.305</v>
+      </c>
+      <c r="M20">
+        <v>0.0143955</v>
+      </c>
+      <c r="N20">
+        <v>0.2906045</v>
+      </c>
+      <c r="O20">
+        <v>0.08427530500000001</v>
+      </c>
+      <c r="P20">
+        <v>0.206329195</v>
+      </c>
+      <c r="Q20">
+        <v>0.206329195</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1963196219512496</v>
+      </c>
+      <c r="T20">
+        <v>0.8353557490550875</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.29</v>
+      </c>
+      <c r="W20">
+        <v>0.032447</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>21.18717654822687</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1663638082876381</v>
+      </c>
+      <c r="C21">
+        <v>1.535432946013072</v>
+      </c>
+      <c r="D21">
+        <v>1.843932946013072</v>
+      </c>
+      <c r="E21">
+        <v>0.3325</v>
+      </c>
+      <c r="F21">
+        <v>0.3325</v>
+      </c>
+      <c r="G21">
+        <v>0.024</v>
+      </c>
+      <c r="H21">
+        <v>1.75</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.305</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0.305</v>
+      </c>
+      <c r="M21">
+        <v>0.01519525</v>
+      </c>
+      <c r="N21">
+        <v>0.28980475</v>
+      </c>
+      <c r="O21">
+        <v>0.08404337750000002</v>
+      </c>
+      <c r="P21">
+        <v>0.2057613725</v>
+      </c>
+      <c r="Q21">
+        <v>0.2057613725</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1977763929477013</v>
+      </c>
+      <c r="T21">
+        <v>0.8430812756394467</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.29</v>
+      </c>
+      <c r="W21">
+        <v>0.032447</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>20.07206199305704</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1659050665752514</v>
+      </c>
+      <c r="C22">
+        <v>1.524587983298147</v>
+      </c>
+      <c r="D22">
+        <v>1.850587983298147</v>
+      </c>
+      <c r="E22">
+        <v>0.35</v>
+      </c>
+      <c r="F22">
+        <v>0.35</v>
+      </c>
+      <c r="G22">
+        <v>0.024</v>
+      </c>
+      <c r="H22">
+        <v>1.75</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.305</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0.305</v>
+      </c>
+      <c r="M22">
+        <v>0.015995</v>
+      </c>
+      <c r="N22">
+        <v>0.289005</v>
+      </c>
+      <c r="O22">
+        <v>0.08381145000000001</v>
+      </c>
+      <c r="P22">
+        <v>0.20519355</v>
+      </c>
+      <c r="Q22">
+        <v>0.20519355</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1992695832190642</v>
+      </c>
+      <c r="T22">
+        <v>0.850999940388415</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.29</v>
+      </c>
+      <c r="W22">
+        <v>0.032447</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>19.06845889340419</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1654463248628647</v>
+      </c>
+      <c r="C23">
+        <v>1.513791232692077</v>
+      </c>
+      <c r="D23">
+        <v>1.857291232692077</v>
+      </c>
+      <c r="E23">
+        <v>0.3675</v>
+      </c>
+      <c r="F23">
+        <v>0.3675</v>
+      </c>
+      <c r="G23">
+        <v>0.024</v>
+      </c>
+      <c r="H23">
+        <v>1.75</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.305</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0.305</v>
+      </c>
+      <c r="M23">
+        <v>0.01679475</v>
+      </c>
+      <c r="N23">
+        <v>0.28820525</v>
+      </c>
+      <c r="O23">
+        <v>0.0835795225</v>
+      </c>
+      <c r="P23">
+        <v>0.2046257275</v>
+      </c>
+      <c r="Q23">
+        <v>0.2046257275</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2008005757757781</v>
+      </c>
+      <c r="T23">
+        <v>0.8591190776626735</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.29</v>
+      </c>
+      <c r="W23">
+        <v>0.032447</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>18.16043704133732</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1649875831504781</v>
+      </c>
+      <c r="C24">
+        <v>1.503043220005043</v>
+      </c>
+      <c r="D24">
+        <v>1.864043220005043</v>
+      </c>
+      <c r="E24">
+        <v>0.385</v>
+      </c>
+      <c r="F24">
+        <v>0.385</v>
+      </c>
+      <c r="G24">
+        <v>0.024</v>
+      </c>
+      <c r="H24">
+        <v>1.75</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.305</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0.305</v>
+      </c>
+      <c r="M24">
+        <v>0.0175945</v>
+      </c>
+      <c r="N24">
+        <v>0.2874055</v>
+      </c>
+      <c r="O24">
+        <v>0.08334759500000001</v>
+      </c>
+      <c r="P24">
+        <v>0.204057905</v>
+      </c>
+      <c r="Q24">
+        <v>0.204057905</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.202370824551895</v>
+      </c>
+      <c r="T24">
+        <v>0.8674463979439644</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.29</v>
+      </c>
+      <c r="W24">
+        <v>0.032447</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>17.33496263036744</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1645288414380915</v>
+      </c>
+      <c r="C25">
+        <v>1.492344478721237</v>
+      </c>
+      <c r="D25">
+        <v>1.870844478721237</v>
+      </c>
+      <c r="E25">
+        <v>0.4025</v>
+      </c>
+      <c r="F25">
+        <v>0.4025</v>
+      </c>
+      <c r="G25">
+        <v>0.024</v>
+      </c>
+      <c r="H25">
+        <v>1.75</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.305</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0.305</v>
+      </c>
+      <c r="M25">
+        <v>0.01839425</v>
+      </c>
+      <c r="N25">
+        <v>0.28660575</v>
+      </c>
+      <c r="O25">
+        <v>0.0831156675</v>
+      </c>
+      <c r="P25">
+        <v>0.2034900825</v>
+      </c>
+      <c r="Q25">
+        <v>0.2034900825</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2039818590105084</v>
+      </c>
+      <c r="T25">
+        <v>0.8759900122585356</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.29</v>
+      </c>
+      <c r="W25">
+        <v>0.032447</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>16.58126860296016</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1640700997257048</v>
+      </c>
+      <c r="C26">
+        <v>1.481695550139372</v>
+      </c>
+      <c r="D26">
+        <v>1.877695550139372</v>
+      </c>
+      <c r="E26">
+        <v>0.42</v>
+      </c>
+      <c r="F26">
+        <v>0.42</v>
+      </c>
+      <c r="G26">
+        <v>0.024</v>
+      </c>
+      <c r="H26">
+        <v>1.75</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.305</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0.305</v>
+      </c>
+      <c r="M26">
+        <v>0.019194</v>
+      </c>
+      <c r="N26">
+        <v>0.285806</v>
+      </c>
+      <c r="O26">
+        <v>0.08288374000000001</v>
+      </c>
+      <c r="P26">
+        <v>0.20292226</v>
+      </c>
+      <c r="Q26">
+        <v>0.20292226</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2056352891127694</v>
+      </c>
+      <c r="T26">
+        <v>0.8847584585287532</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.29</v>
+      </c>
+      <c r="W26">
+        <v>0.032447</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>15.89038241117015</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1636113580133181</v>
+      </c>
+      <c r="C27">
+        <v>1.471096983516291</v>
+      </c>
+      <c r="D27">
+        <v>1.884596983516291</v>
+      </c>
+      <c r="E27">
+        <v>0.4375</v>
+      </c>
+      <c r="F27">
+        <v>0.4375</v>
+      </c>
+      <c r="G27">
+        <v>0.024</v>
+      </c>
+      <c r="H27">
+        <v>1.75</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.305</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0.305</v>
+      </c>
+      <c r="M27">
+        <v>0.01999375</v>
+      </c>
+      <c r="N27">
+        <v>0.28500625</v>
+      </c>
+      <c r="O27">
+        <v>0.08265181250000002</v>
+      </c>
+      <c r="P27">
+        <v>0.2023544375</v>
+      </c>
+      <c r="Q27">
+        <v>0.2023544375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2073328106844241</v>
+      </c>
+      <c r="T27">
+        <v>0.8937607300328434</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.29</v>
+      </c>
+      <c r="W27">
+        <v>0.032447</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>15.25476711472335</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1631526163009315</v>
+      </c>
+      <c r="C28">
+        <v>1.460549336213759</v>
+      </c>
+      <c r="D28">
+        <v>1.891549336213759</v>
+      </c>
+      <c r="E28">
+        <v>0.455</v>
+      </c>
+      <c r="F28">
+        <v>0.455</v>
+      </c>
+      <c r="G28">
+        <v>0.024</v>
+      </c>
+      <c r="H28">
+        <v>1.75</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.305</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0.305</v>
+      </c>
+      <c r="M28">
+        <v>0.0207935</v>
+      </c>
+      <c r="N28">
+        <v>0.2842065</v>
+      </c>
+      <c r="O28">
+        <v>0.082419885</v>
+      </c>
+      <c r="P28">
+        <v>0.201786615</v>
+      </c>
+      <c r="Q28">
+        <v>0.201786615</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.209076211217475</v>
+      </c>
+      <c r="T28">
+        <v>0.9030063061721794</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.29</v>
+      </c>
+      <c r="W28">
+        <v>0.032447</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>14.6680453026186</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1626938745885448</v>
+      </c>
+      <c r="C29">
+        <v>1.450053173848512</v>
+      </c>
+      <c r="D29">
+        <v>1.898553173848512</v>
+      </c>
+      <c r="E29">
+        <v>0.4725</v>
+      </c>
+      <c r="F29">
+        <v>0.4725</v>
+      </c>
+      <c r="G29">
+        <v>0.024</v>
+      </c>
+      <c r="H29">
+        <v>1.75</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.305</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0.305</v>
+      </c>
+      <c r="M29">
+        <v>0.02159325</v>
+      </c>
+      <c r="N29">
+        <v>0.28340675</v>
+      </c>
+      <c r="O29">
+        <v>0.08218795750000001</v>
+      </c>
+      <c r="P29">
+        <v>0.2012187925</v>
+      </c>
+      <c r="Q29">
+        <v>0.2012187925</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2108673761486915</v>
+      </c>
+      <c r="T29">
+        <v>0.9125051857673874</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.29</v>
+      </c>
+      <c r="W29">
+        <v>0.032447</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>14.12478436548458</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1622351328761582</v>
+      </c>
+      <c r="C30">
+        <v>1.439609070445651</v>
+      </c>
+      <c r="D30">
+        <v>1.905609070445651</v>
+      </c>
+      <c r="E30">
+        <v>0.49</v>
+      </c>
+      <c r="F30">
+        <v>0.49</v>
+      </c>
+      <c r="G30">
+        <v>0.024</v>
+      </c>
+      <c r="H30">
+        <v>1.75</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.305</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0.305</v>
+      </c>
+      <c r="M30">
+        <v>0.022393</v>
+      </c>
+      <c r="N30">
+        <v>0.282607</v>
+      </c>
+      <c r="O30">
+        <v>0.08195603000000001</v>
+      </c>
+      <c r="P30">
+        <v>0.20065097</v>
+      </c>
+      <c r="Q30">
+        <v>0.20065097</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2127082956613308</v>
+      </c>
+      <c r="T30">
+        <v>0.9222679231291292</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.29</v>
+      </c>
+      <c r="W30">
+        <v>0.032447</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>13.62032778100299</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1617763911637715</v>
+      </c>
+      <c r="C31">
+        <v>1.429217608595479</v>
+      </c>
+      <c r="D31">
+        <v>1.912717608595479</v>
+      </c>
+      <c r="E31">
+        <v>0.5075</v>
+      </c>
+      <c r="F31">
+        <v>0.5075</v>
+      </c>
+      <c r="G31">
+        <v>0.024</v>
+      </c>
+      <c r="H31">
+        <v>1.75</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.305</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0.305</v>
+      </c>
+      <c r="M31">
+        <v>0.02319275</v>
+      </c>
+      <c r="N31">
+        <v>0.28180725</v>
+      </c>
+      <c r="O31">
+        <v>0.08172410250000001</v>
+      </c>
+      <c r="P31">
+        <v>0.2000831475</v>
+      </c>
+      <c r="Q31">
+        <v>0.2000831475</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.21460107206165</v>
+      </c>
+      <c r="T31">
+        <v>0.932305667177117</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.29</v>
+      </c>
+      <c r="W31">
+        <v>0.032447</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>13.15066130579599</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1616584494513848</v>
+      </c>
+      <c r="C32">
+        <v>1.413553780149631</v>
+      </c>
+      <c r="D32">
+        <v>1.914553780149632</v>
+      </c>
+      <c r="E32">
+        <v>0.525</v>
+      </c>
+      <c r="F32">
+        <v>0.525</v>
+      </c>
+      <c r="G32">
+        <v>0.024</v>
+      </c>
+      <c r="H32">
+        <v>1.75</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.305</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0.305</v>
+      </c>
+      <c r="M32">
+        <v>0.0248325</v>
+      </c>
+      <c r="N32">
+        <v>0.2801675</v>
+      </c>
+      <c r="O32">
+        <v>0.08124857500000002</v>
+      </c>
+      <c r="P32">
+        <v>0.198918925</v>
+      </c>
+      <c r="Q32">
+        <v>0.198918925</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2165479277876926</v>
+      </c>
+      <c r="T32">
+        <v>0.9426302039121903</v>
+      </c>
+      <c r="U32">
+        <v>0.0473</v>
+      </c>
+      <c r="V32">
+        <v>0.29</v>
+      </c>
+      <c r="W32">
+        <v>0.033583</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>12.28229135205879</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1612110677389982</v>
+      </c>
+      <c r="C33">
+        <v>1.403050993428139</v>
+      </c>
+      <c r="D33">
+        <v>1.921550993428139</v>
+      </c>
+      <c r="E33">
+        <v>0.5425</v>
+      </c>
+      <c r="F33">
+        <v>0.5425</v>
+      </c>
+      <c r="G33">
+        <v>0.024</v>
+      </c>
+      <c r="H33">
+        <v>1.75</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.305</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0.305</v>
+      </c>
+      <c r="M33">
+        <v>0.02566025</v>
+      </c>
+      <c r="N33">
+        <v>0.27933975</v>
+      </c>
+      <c r="O33">
+        <v>0.08100852750000001</v>
+      </c>
+      <c r="P33">
+        <v>0.1983312225</v>
+      </c>
+      <c r="Q33">
+        <v>0.1983312225</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2185512141144901</v>
+      </c>
+      <c r="T33">
+        <v>0.9532540025816135</v>
+      </c>
+      <c r="U33">
+        <v>0.0473</v>
+      </c>
+      <c r="V33">
+        <v>0.29</v>
+      </c>
+      <c r="W33">
+        <v>0.033583</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>11.88608840521819</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1607636860266115</v>
+      </c>
+      <c r="C34">
+        <v>1.392599540433275</v>
+      </c>
+      <c r="D34">
+        <v>1.928599540433275</v>
+      </c>
+      <c r="E34">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F34">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.024</v>
+      </c>
+      <c r="H34">
+        <v>1.75</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.305</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0.305</v>
+      </c>
+      <c r="M34">
+        <v>0.026488</v>
+      </c>
+      <c r="N34">
+        <v>0.278512</v>
+      </c>
+      <c r="O34">
+        <v>0.08076848</v>
+      </c>
+      <c r="P34">
+        <v>0.19774352</v>
+      </c>
+      <c r="Q34">
+        <v>0.19774352</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2206134206273699</v>
+      </c>
+      <c r="T34">
+        <v>0.9641902659177846</v>
+      </c>
+      <c r="U34">
+        <v>0.0473</v>
+      </c>
+      <c r="V34">
+        <v>0.29</v>
+      </c>
+      <c r="W34">
+        <v>0.033583</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>11.51464814255512</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1603163043142249</v>
+      </c>
+      <c r="C35">
+        <v>1.382199988145016</v>
+      </c>
+      <c r="D35">
+        <v>1.935699988145016</v>
+      </c>
+      <c r="E35">
+        <v>0.5775</v>
+      </c>
+      <c r="F35">
+        <v>0.5775</v>
+      </c>
+      <c r="G35">
+        <v>0.024</v>
+      </c>
+      <c r="H35">
+        <v>1.75</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.305</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0.305</v>
+      </c>
+      <c r="M35">
+        <v>0.02731575</v>
+      </c>
+      <c r="N35">
+        <v>0.27768425</v>
+      </c>
+      <c r="O35">
+        <v>0.0805284325</v>
+      </c>
+      <c r="P35">
+        <v>0.1971558175</v>
+      </c>
+      <c r="Q35">
+        <v>0.1971558175</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2227371855436192</v>
+      </c>
+      <c r="T35">
+        <v>0.9754529848759307</v>
+      </c>
+      <c r="U35">
+        <v>0.0473</v>
+      </c>
+      <c r="V35">
+        <v>0.29</v>
+      </c>
+      <c r="W35">
+        <v>0.033583</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>11.16571941096254</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1598689226018382</v>
+      </c>
+      <c r="C36">
+        <v>1.371852911923905</v>
+      </c>
+      <c r="D36">
+        <v>1.942852911923905</v>
+      </c>
+      <c r="E36">
+        <v>0.5950000000000001</v>
+      </c>
+      <c r="F36">
+        <v>0.5950000000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.024</v>
+      </c>
+      <c r="H36">
+        <v>1.75</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.305</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0.305</v>
+      </c>
+      <c r="M36">
+        <v>0.02814350000000001</v>
+      </c>
+      <c r="N36">
+        <v>0.2768565</v>
+      </c>
+      <c r="O36">
+        <v>0.08028838500000002</v>
+      </c>
+      <c r="P36">
+        <v>0.196568115</v>
+      </c>
+      <c r="Q36">
+        <v>0.196568115</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2249253069724821</v>
+      </c>
+      <c r="T36">
+        <v>0.9870569983479601</v>
+      </c>
+      <c r="U36">
+        <v>0.0473</v>
+      </c>
+      <c r="V36">
+        <v>0.29</v>
+      </c>
+      <c r="W36">
+        <v>0.033583</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>10.8373158988754</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1594215408894515</v>
+      </c>
+      <c r="C37">
+        <v>1.361558895666465</v>
+      </c>
+      <c r="D37">
+        <v>1.950058895666465</v>
+      </c>
+      <c r="E37">
+        <v>0.6125</v>
+      </c>
+      <c r="F37">
+        <v>0.6125</v>
+      </c>
+      <c r="G37">
+        <v>0.024</v>
+      </c>
+      <c r="H37">
+        <v>1.75</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.305</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0.305</v>
+      </c>
+      <c r="M37">
+        <v>0.02897125</v>
+      </c>
+      <c r="N37">
+        <v>0.27602875</v>
+      </c>
+      <c r="O37">
+        <v>0.08004833750000001</v>
+      </c>
+      <c r="P37">
+        <v>0.1959804125</v>
+      </c>
+      <c r="Q37">
+        <v>0.1959804125</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2271807552145409</v>
+      </c>
+      <c r="T37">
+        <v>0.9990180583883599</v>
+      </c>
+      <c r="U37">
+        <v>0.0473</v>
+      </c>
+      <c r="V37">
+        <v>0.29</v>
+      </c>
+      <c r="W37">
+        <v>0.033583</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>10.52767830176468</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1599454391770649</v>
+      </c>
+      <c r="C38">
+        <v>1.335625788129567</v>
+      </c>
+      <c r="D38">
+        <v>1.941625788129567</v>
+      </c>
+      <c r="E38">
+        <v>0.63</v>
+      </c>
+      <c r="F38">
+        <v>0.63</v>
+      </c>
+      <c r="G38">
+        <v>0.024</v>
+      </c>
+      <c r="H38">
+        <v>1.75</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.305</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0.305</v>
+      </c>
+      <c r="M38">
+        <v>0.032193</v>
+      </c>
+      <c r="N38">
+        <v>0.272807</v>
+      </c>
+      <c r="O38">
+        <v>0.07911403000000002</v>
+      </c>
+      <c r="P38">
+        <v>0.19369297</v>
+      </c>
+      <c r="Q38">
+        <v>0.19369297</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2295066862141639</v>
+      </c>
+      <c r="T38">
+        <v>1.011352901555022</v>
+      </c>
+      <c r="U38">
+        <v>0.0511</v>
+      </c>
+      <c r="V38">
+        <v>0.29</v>
+      </c>
+      <c r="W38">
+        <v>0.036281</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>9.474109278414563</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1595250374646782</v>
+      </c>
+      <c r="C39">
+        <v>1.324887126318281</v>
+      </c>
+      <c r="D39">
+        <v>1.948387126318281</v>
+      </c>
+      <c r="E39">
+        <v>0.6475</v>
+      </c>
+      <c r="F39">
+        <v>0.6475</v>
+      </c>
+      <c r="G39">
+        <v>0.024</v>
+      </c>
+      <c r="H39">
+        <v>1.75</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.305</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0.305</v>
+      </c>
+      <c r="M39">
+        <v>0.03308725</v>
+      </c>
+      <c r="N39">
+        <v>0.27191275</v>
+      </c>
+      <c r="O39">
+        <v>0.0788546975</v>
+      </c>
+      <c r="P39">
+        <v>0.1930580525</v>
+      </c>
+      <c r="Q39">
+        <v>0.1930580525</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2319064562931401</v>
+      </c>
+      <c r="T39">
+        <v>1.024079327044435</v>
+      </c>
+      <c r="U39">
+        <v>0.0511</v>
+      </c>
+      <c r="V39">
+        <v>0.29</v>
+      </c>
+      <c r="W39">
+        <v>0.036281</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>9.218052270889844</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1591046357522916</v>
+      </c>
+      <c r="C40">
+        <v>1.314195719180677</v>
+      </c>
+      <c r="D40">
+        <v>1.955195719180677</v>
+      </c>
+      <c r="E40">
+        <v>0.665</v>
+      </c>
+      <c r="F40">
+        <v>0.665</v>
+      </c>
+      <c r="G40">
+        <v>0.024</v>
+      </c>
+      <c r="H40">
+        <v>1.75</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.305</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0.305</v>
+      </c>
+      <c r="M40">
+        <v>0.0339815</v>
+      </c>
+      <c r="N40">
+        <v>0.2710185</v>
+      </c>
+      <c r="O40">
+        <v>0.07859536500000001</v>
+      </c>
+      <c r="P40">
+        <v>0.192423135</v>
+      </c>
+      <c r="Q40">
+        <v>0.192423135</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2343836383101477</v>
+      </c>
+      <c r="T40">
+        <v>1.037216282388346</v>
+      </c>
+      <c r="U40">
+        <v>0.0511</v>
+      </c>
+      <c r="V40">
+        <v>0.29</v>
+      </c>
+      <c r="W40">
+        <v>0.036281</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>8.975471947971689</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1586842340399049</v>
+      </c>
+      <c r="C41">
+        <v>1.30355206384499</v>
+      </c>
+      <c r="D41">
+        <v>1.96205206384499</v>
+      </c>
+      <c r="E41">
+        <v>0.6825</v>
+      </c>
+      <c r="F41">
+        <v>0.6825</v>
+      </c>
+      <c r="G41">
+        <v>0.024</v>
+      </c>
+      <c r="H41">
+        <v>1.75</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.305</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0.305</v>
+      </c>
+      <c r="M41">
+        <v>0.03487575</v>
+      </c>
+      <c r="N41">
+        <v>0.27012425</v>
+      </c>
+      <c r="O41">
+        <v>0.07833603250000001</v>
+      </c>
+      <c r="P41">
+        <v>0.1917882175</v>
+      </c>
+      <c r="Q41">
+        <v>0.1917882175</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2369420394096802</v>
+      </c>
+      <c r="T41">
+        <v>1.050783957579597</v>
+      </c>
+      <c r="U41">
+        <v>0.0511</v>
+      </c>
+      <c r="V41">
+        <v>0.29</v>
+      </c>
+      <c r="W41">
+        <v>0.036281</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>8.745331641613443</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1582638323275183</v>
+      </c>
+      <c r="C42">
+        <v>1.292956664437166</v>
+      </c>
+      <c r="D42">
+        <v>1.968956664437165</v>
+      </c>
+      <c r="E42">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="F42">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.024</v>
+      </c>
+      <c r="H42">
+        <v>1.75</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.305</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0.305</v>
+      </c>
+      <c r="M42">
+        <v>0.03577</v>
+      </c>
+      <c r="N42">
+        <v>0.26923</v>
+      </c>
+      <c r="O42">
+        <v>0.0780767</v>
+      </c>
+      <c r="P42">
+        <v>0.1911533</v>
+      </c>
+      <c r="Q42">
+        <v>0.1911533</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2395857205458638</v>
+      </c>
+      <c r="T42">
+        <v>1.064803888610558</v>
+      </c>
+      <c r="U42">
+        <v>0.0511</v>
+      </c>
+      <c r="V42">
+        <v>0.29</v>
+      </c>
+      <c r="W42">
+        <v>0.036281</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>8.526698350573104</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1578434306151316</v>
+      </c>
+      <c r="C43">
+        <v>1.282410032204436</v>
+      </c>
+      <c r="D43">
+        <v>1.975910032204436</v>
+      </c>
+      <c r="E43">
+        <v>0.7175</v>
+      </c>
+      <c r="F43">
+        <v>0.7175</v>
+      </c>
+      <c r="G43">
+        <v>0.024</v>
+      </c>
+      <c r="H43">
+        <v>1.75</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.305</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0.305</v>
+      </c>
+      <c r="M43">
+        <v>0.03666425</v>
+      </c>
+      <c r="N43">
+        <v>0.26833575</v>
+      </c>
+      <c r="O43">
+        <v>0.0778173675</v>
+      </c>
+      <c r="P43">
+        <v>0.1905183825</v>
+      </c>
+      <c r="Q43">
+        <v>0.1905183825</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2423190179917485</v>
+      </c>
+      <c r="T43">
+        <v>1.079299071540872</v>
+      </c>
+      <c r="U43">
+        <v>0.0511</v>
+      </c>
+      <c r="V43">
+        <v>0.29</v>
+      </c>
+      <c r="W43">
+        <v>0.036281</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>8.318730098120103</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.157423028902745</v>
+      </c>
+      <c r="C44">
+        <v>1.271912685641499</v>
+      </c>
+      <c r="D44">
+        <v>1.982912685641499</v>
+      </c>
+      <c r="E44">
+        <v>0.735</v>
+      </c>
+      <c r="F44">
+        <v>0.735</v>
+      </c>
+      <c r="G44">
+        <v>0.024</v>
+      </c>
+      <c r="H44">
+        <v>1.75</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.305</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0.305</v>
+      </c>
+      <c r="M44">
+        <v>0.0375585</v>
+      </c>
+      <c r="N44">
+        <v>0.2674415</v>
+      </c>
+      <c r="O44">
+        <v>0.07755803500000001</v>
+      </c>
+      <c r="P44">
+        <v>0.189883465</v>
+      </c>
+      <c r="Q44">
+        <v>0.189883465</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2451465670736982</v>
+      </c>
+      <c r="T44">
+        <v>1.094294088365336</v>
+      </c>
+      <c r="U44">
+        <v>0.0511</v>
+      </c>
+      <c r="V44">
+        <v>0.29</v>
+      </c>
+      <c r="W44">
+        <v>0.036281</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>8.120665095783909</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1570026271903583</v>
+      </c>
+      <c r="C45">
+        <v>1.261465150619408</v>
+      </c>
+      <c r="D45">
+        <v>1.989965150619408</v>
+      </c>
+      <c r="E45">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="F45">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="G45">
+        <v>0.024</v>
+      </c>
+      <c r="H45">
+        <v>1.75</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.305</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0.305</v>
+      </c>
+      <c r="M45">
+        <v>0.03845274999999999</v>
+      </c>
+      <c r="N45">
+        <v>0.26654725</v>
+      </c>
+      <c r="O45">
+        <v>0.07729870250000001</v>
+      </c>
+      <c r="P45">
+        <v>0.1892485475</v>
+      </c>
+      <c r="Q45">
+        <v>0.1892485475</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2480733284041374</v>
+      </c>
+      <c r="T45">
+        <v>1.109815246131008</v>
+      </c>
+      <c r="U45">
+        <v>0.0511</v>
+      </c>
+      <c r="V45">
+        <v>0.29</v>
+      </c>
+      <c r="W45">
+        <v>0.036281</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>7.931812419137774</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1571757854779717</v>
+      </c>
+      <c r="C46">
+        <v>1.241054260047488</v>
+      </c>
+      <c r="D46">
+        <v>1.987054260047488</v>
+      </c>
+      <c r="E46">
+        <v>0.77</v>
+      </c>
+      <c r="F46">
+        <v>0.77</v>
+      </c>
+      <c r="G46">
+        <v>0.024</v>
+      </c>
+      <c r="H46">
+        <v>1.75</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.305</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0.305</v>
+      </c>
+      <c r="M46">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="N46">
+        <v>0.26419</v>
+      </c>
+      <c r="O46">
+        <v>0.07661510000000001</v>
+      </c>
+      <c r="P46">
+        <v>0.1875749</v>
+      </c>
+      <c r="Q46">
+        <v>0.1875749</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2511046169249495</v>
+      </c>
+      <c r="T46">
+        <v>1.125890730959741</v>
+      </c>
+      <c r="U46">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.29</v>
+      </c>
+      <c r="W46">
+        <v>0.03763</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>7.473658417054642</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.156768873765585</v>
+      </c>
+      <c r="C47">
+        <v>1.230408234538826</v>
+      </c>
+      <c r="D47">
+        <v>1.993908234538826</v>
+      </c>
+      <c r="E47">
+        <v>0.7875</v>
+      </c>
+      <c r="F47">
+        <v>0.7875</v>
+      </c>
+      <c r="G47">
+        <v>0.024</v>
+      </c>
+      <c r="H47">
+        <v>1.75</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.305</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0.305</v>
+      </c>
+      <c r="M47">
+        <v>0.0417375</v>
+      </c>
+      <c r="N47">
+        <v>0.2632625</v>
+      </c>
+      <c r="O47">
+        <v>0.07634612500000001</v>
+      </c>
+      <c r="P47">
+        <v>0.186916375</v>
+      </c>
+      <c r="Q47">
+        <v>0.186916375</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2542461341192455</v>
+      </c>
+      <c r="T47">
+        <v>1.142550778873155</v>
+      </c>
+      <c r="U47">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.29</v>
+      </c>
+      <c r="W47">
+        <v>0.03763</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>7.307577118897873</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1563619620531984</v>
+      </c>
+      <c r="C48">
+        <v>1.219809655711865</v>
+      </c>
+      <c r="D48">
+        <v>2.000809655711865</v>
+      </c>
+      <c r="E48">
+        <v>0.805</v>
+      </c>
+      <c r="F48">
+        <v>0.805</v>
+      </c>
+      <c r="G48">
+        <v>0.024</v>
+      </c>
+      <c r="H48">
+        <v>1.75</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.305</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0.305</v>
+      </c>
+      <c r="M48">
+        <v>0.04266500000000001</v>
+      </c>
+      <c r="N48">
+        <v>0.262335</v>
+      </c>
+      <c r="O48">
+        <v>0.07607715000000001</v>
+      </c>
+      <c r="P48">
+        <v>0.18625785</v>
+      </c>
+      <c r="Q48">
+        <v>0.18625785</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2575040038022192</v>
+      </c>
+      <c r="T48">
+        <v>1.159827865598176</v>
+      </c>
+      <c r="U48">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.29</v>
+      </c>
+      <c r="W48">
+        <v>0.03763</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>7.148716746747918</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1559550503408117</v>
+      </c>
+      <c r="C49">
+        <v>1.209259017952734</v>
+      </c>
+      <c r="D49">
+        <v>2.007759017952734</v>
+      </c>
+      <c r="E49">
+        <v>0.8225</v>
+      </c>
+      <c r="F49">
+        <v>0.8225</v>
+      </c>
+      <c r="G49">
+        <v>0.024</v>
+      </c>
+      <c r="H49">
+        <v>1.75</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.305</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0.305</v>
+      </c>
+      <c r="M49">
+        <v>0.04359250000000001</v>
+      </c>
+      <c r="N49">
+        <v>0.2614075</v>
+      </c>
+      <c r="O49">
+        <v>0.07580817500000002</v>
+      </c>
+      <c r="P49">
+        <v>0.185599325</v>
+      </c>
+      <c r="Q49">
+        <v>0.185599325</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2608848119637956</v>
+      </c>
+      <c r="T49">
+        <v>1.177756917859991</v>
+      </c>
+      <c r="U49">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.29</v>
+      </c>
+      <c r="W49">
+        <v>0.03763</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>6.996616390434133</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1555481386284251</v>
+      </c>
+      <c r="C50">
+        <v>1.198756822540052</v>
+      </c>
+      <c r="D50">
+        <v>2.014756822540052</v>
+      </c>
+      <c r="E50">
+        <v>0.84</v>
+      </c>
+      <c r="F50">
+        <v>0.84</v>
+      </c>
+      <c r="G50">
+        <v>0.024</v>
+      </c>
+      <c r="H50">
+        <v>1.75</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.305</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0.305</v>
+      </c>
+      <c r="M50">
+        <v>0.04452</v>
+      </c>
+      <c r="N50">
+        <v>0.26048</v>
+      </c>
+      <c r="O50">
+        <v>0.0755392</v>
+      </c>
+      <c r="P50">
+        <v>0.1849408</v>
+      </c>
+      <c r="Q50">
+        <v>0.1849408</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2643956512085097</v>
+      </c>
+      <c r="T50">
+        <v>1.196375549054953</v>
+      </c>
+      <c r="U50">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.29</v>
+      </c>
+      <c r="W50">
+        <v>0.03763</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>6.850853548966755</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1551412269160384</v>
+      </c>
+      <c r="C51">
+        <v>1.188303577765474</v>
+      </c>
+      <c r="D51">
+        <v>2.021803577765474</v>
+      </c>
+      <c r="E51">
+        <v>0.8574999999999999</v>
+      </c>
+      <c r="F51">
+        <v>0.8574999999999999</v>
+      </c>
+      <c r="G51">
+        <v>0.024</v>
+      </c>
+      <c r="H51">
+        <v>1.75</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.305</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0.305</v>
+      </c>
+      <c r="M51">
+        <v>0.0454475</v>
+      </c>
+      <c r="N51">
+        <v>0.2595525</v>
+      </c>
+      <c r="O51">
+        <v>0.075270225</v>
+      </c>
+      <c r="P51">
+        <v>0.184282275</v>
+      </c>
+      <c r="Q51">
+        <v>0.184282275</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2680441704236047</v>
+      </c>
+      <c r="T51">
+        <v>1.215724322649717</v>
+      </c>
+      <c r="U51">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.29</v>
+      </c>
+      <c r="W51">
+        <v>0.03763</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>6.71104021123274</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1547343152036517</v>
+      </c>
+      <c r="C52">
+        <v>1.177899799056753</v>
+      </c>
+      <c r="D52">
+        <v>2.028899799056753</v>
+      </c>
+      <c r="E52">
+        <v>0.875</v>
+      </c>
+      <c r="F52">
+        <v>0.875</v>
+      </c>
+      <c r="G52">
+        <v>0.024</v>
+      </c>
+      <c r="H52">
+        <v>1.75</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.305</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0.305</v>
+      </c>
+      <c r="M52">
+        <v>0.04637500000000001</v>
+      </c>
+      <c r="N52">
+        <v>0.258625</v>
+      </c>
+      <c r="O52">
+        <v>0.07500125000000001</v>
+      </c>
+      <c r="P52">
+        <v>0.18362375</v>
+      </c>
+      <c r="Q52">
+        <v>0.18362375</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2718386304073035</v>
+      </c>
+      <c r="T52">
+        <v>1.235847047188271</v>
+      </c>
+      <c r="U52">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.29</v>
+      </c>
+      <c r="W52">
+        <v>0.03763</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>6.576819407008085</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1543274034912651</v>
+      </c>
+      <c r="C53">
+        <v>1.167546009103424</v>
+      </c>
+      <c r="D53">
+        <v>2.036046009103424</v>
+      </c>
+      <c r="E53">
+        <v>0.8925000000000001</v>
+      </c>
+      <c r="F53">
+        <v>0.8925000000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.024</v>
+      </c>
+      <c r="H53">
+        <v>1.75</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.305</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0.305</v>
+      </c>
+      <c r="M53">
+        <v>0.04730250000000001</v>
+      </c>
+      <c r="N53">
+        <v>0.2576975</v>
+      </c>
+      <c r="O53">
+        <v>0.074732275</v>
+      </c>
+      <c r="P53">
+        <v>0.182965225</v>
+      </c>
+      <c r="Q53">
+        <v>0.182965225</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2757879663087043</v>
+      </c>
+      <c r="T53">
+        <v>1.256791107422277</v>
+      </c>
+      <c r="U53">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.29</v>
+      </c>
+      <c r="W53">
+        <v>0.03763</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>6.447862163733416</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1539204917788784</v>
+      </c>
+      <c r="C54">
+        <v>1.157242737985139</v>
+      </c>
+      <c r="D54">
+        <v>2.043242737985139</v>
+      </c>
+      <c r="E54">
+        <v>0.91</v>
+      </c>
+      <c r="F54">
+        <v>0.91</v>
+      </c>
+      <c r="G54">
+        <v>0.024</v>
+      </c>
+      <c r="H54">
+        <v>1.75</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.305</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0.305</v>
+      </c>
+      <c r="M54">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="N54">
+        <v>0.25677</v>
+      </c>
+      <c r="O54">
+        <v>0.07446330000000001</v>
+      </c>
+      <c r="P54">
+        <v>0.1823067</v>
+      </c>
+      <c r="Q54">
+        <v>0.1823067</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2799018578726634</v>
+      </c>
+      <c r="T54">
+        <v>1.2786078368327</v>
+      </c>
+      <c r="U54">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.29</v>
+      </c>
+      <c r="W54">
+        <v>0.03763</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>6.323864814430851</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1542661800664918</v>
+      </c>
+      <c r="C55">
+        <v>1.133625578113168</v>
+      </c>
+      <c r="D55">
+        <v>2.037125578113168</v>
+      </c>
+      <c r="E55">
+        <v>0.9275</v>
+      </c>
+      <c r="F55">
+        <v>0.9275</v>
+      </c>
+      <c r="G55">
+        <v>0.024</v>
+      </c>
+      <c r="H55">
+        <v>1.75</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.305</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0.305</v>
+      </c>
+      <c r="M55">
+        <v>0.0510125</v>
+      </c>
+      <c r="N55">
+        <v>0.2539875</v>
+      </c>
+      <c r="O55">
+        <v>0.073656375</v>
+      </c>
+      <c r="P55">
+        <v>0.180331125</v>
+      </c>
+      <c r="Q55">
+        <v>0.180331125</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2841908086521102</v>
+      </c>
+      <c r="T55">
+        <v>1.301352937707396</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.29</v>
+      </c>
+      <c r="W55">
+        <v>0.03905</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>5.978926733643714</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1538734683541051</v>
+      </c>
+      <c r="C56">
+        <v>1.123077685193713</v>
+      </c>
+      <c r="D56">
+        <v>2.044077685193713</v>
+      </c>
+      <c r="E56">
+        <v>0.9450000000000001</v>
+      </c>
+      <c r="F56">
+        <v>0.9450000000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.024</v>
+      </c>
+      <c r="H56">
+        <v>1.75</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.305</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0.305</v>
+      </c>
+      <c r="M56">
+        <v>0.051975</v>
+      </c>
+      <c r="N56">
+        <v>0.253025</v>
+      </c>
+      <c r="O56">
+        <v>0.07337725</v>
+      </c>
+      <c r="P56">
+        <v>0.17964775</v>
+      </c>
+      <c r="Q56">
+        <v>0.17964775</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2886662355524025</v>
+      </c>
+      <c r="T56">
+        <v>1.325086956011426</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.29</v>
+      </c>
+      <c r="W56">
+        <v>0.03905</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>5.868205868205868</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1534807566417185</v>
+      </c>
+      <c r="C57">
+        <v>1.112577405735422</v>
+      </c>
+      <c r="D57">
+        <v>2.051077405735422</v>
+      </c>
+      <c r="E57">
+        <v>0.9625000000000001</v>
+      </c>
+      <c r="F57">
+        <v>0.9625000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.024</v>
+      </c>
+      <c r="H57">
+        <v>1.75</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.305</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0.305</v>
+      </c>
+      <c r="M57">
+        <v>0.05293750000000001</v>
+      </c>
+      <c r="N57">
+        <v>0.2520625</v>
+      </c>
+      <c r="O57">
+        <v>0.073098125</v>
+      </c>
+      <c r="P57">
+        <v>0.178964375</v>
+      </c>
+      <c r="Q57">
+        <v>0.178964375</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2933405703149299</v>
+      </c>
+      <c r="T57">
+        <v>1.349875819573414</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.29</v>
+      </c>
+      <c r="W57">
+        <v>0.03905</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.76151121605667</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1530880449293318</v>
+      </c>
+      <c r="C58">
+        <v>1.102125230560338</v>
+      </c>
+      <c r="D58">
+        <v>2.058125230560337</v>
+      </c>
+      <c r="E58">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="F58">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.024</v>
+      </c>
+      <c r="H58">
+        <v>1.75</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.305</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0.305</v>
+      </c>
+      <c r="M58">
+        <v>0.0539</v>
+      </c>
+      <c r="N58">
+        <v>0.2511</v>
+      </c>
+      <c r="O58">
+        <v>0.07281900000000001</v>
+      </c>
+      <c r="P58">
+        <v>0.178281</v>
+      </c>
+      <c r="Q58">
+        <v>0.178281</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2982273748393905</v>
+      </c>
+      <c r="T58">
+        <v>1.375791449660947</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.29</v>
+      </c>
+      <c r="W58">
+        <v>0.03905</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.658627087198515</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1526953332169452</v>
+      </c>
+      <c r="C59">
+        <v>1.091721657259928</v>
+      </c>
+      <c r="D59">
+        <v>2.065221657259928</v>
+      </c>
+      <c r="E59">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="F59">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.024</v>
+      </c>
+      <c r="H59">
+        <v>1.75</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.305</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0.305</v>
+      </c>
+      <c r="M59">
+        <v>0.0548625</v>
+      </c>
+      <c r="N59">
+        <v>0.2501375</v>
+      </c>
+      <c r="O59">
+        <v>0.07253987500000002</v>
+      </c>
+      <c r="P59">
+        <v>0.177597625</v>
+      </c>
+      <c r="Q59">
+        <v>0.177597625</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3033414725975469</v>
+      </c>
+      <c r="T59">
+        <v>1.402912457892085</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.29</v>
+      </c>
+      <c r="W59">
+        <v>0.03905</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.559352927773981</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1523026215045585</v>
+      </c>
+      <c r="C60">
+        <v>1.081367190312202</v>
+      </c>
+      <c r="D60">
+        <v>2.072367190312202</v>
+      </c>
+      <c r="E60">
+        <v>1.015</v>
+      </c>
+      <c r="F60">
+        <v>1.015</v>
+      </c>
+      <c r="G60">
+        <v>0.024</v>
+      </c>
+      <c r="H60">
+        <v>1.75</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.305</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0.305</v>
+      </c>
+      <c r="M60">
+        <v>0.05582499999999999</v>
+      </c>
+      <c r="N60">
+        <v>0.249175</v>
+      </c>
+      <c r="O60">
+        <v>0.07226075000000001</v>
+      </c>
+      <c r="P60">
+        <v>0.17691425</v>
+      </c>
+      <c r="Q60">
+        <v>0.17691425</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3086990988203774</v>
+      </c>
+      <c r="T60">
+        <v>1.431324942705659</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.29</v>
+      </c>
+      <c r="W60">
+        <v>0.03905</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>5.463502015226154</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1519099097921718</v>
+      </c>
+      <c r="C61">
+        <v>1.071062341201252</v>
+      </c>
+      <c r="D61">
+        <v>2.079562341201252</v>
+      </c>
+      <c r="E61">
+        <v>1.0325</v>
+      </c>
+      <c r="F61">
+        <v>1.0325</v>
+      </c>
+      <c r="G61">
+        <v>0.024</v>
+      </c>
+      <c r="H61">
+        <v>1.75</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.305</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0.305</v>
+      </c>
+      <c r="M61">
+        <v>0.0567875</v>
+      </c>
+      <c r="N61">
+        <v>0.2482125</v>
+      </c>
+      <c r="O61">
+        <v>0.07198162500000001</v>
+      </c>
+      <c r="P61">
+        <v>0.176230875</v>
+      </c>
+      <c r="Q61">
+        <v>0.176230875</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3143180726638337</v>
+      </c>
+      <c r="T61">
+        <v>1.461123402388187</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.29</v>
+      </c>
+      <c r="W61">
+        <v>0.03905</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>5.370900286154524</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1515171980797852</v>
+      </c>
+      <c r="C62">
+        <v>1.060807628539302</v>
+      </c>
+      <c r="D62">
+        <v>2.086807628539302</v>
+      </c>
+      <c r="E62">
+        <v>1.05</v>
+      </c>
+      <c r="F62">
+        <v>1.05</v>
+      </c>
+      <c r="G62">
+        <v>0.024</v>
+      </c>
+      <c r="H62">
+        <v>1.75</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.305</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0.305</v>
+      </c>
+      <c r="M62">
+        <v>0.05775</v>
+      </c>
+      <c r="N62">
+        <v>0.24725</v>
+      </c>
+      <c r="O62">
+        <v>0.0717025</v>
+      </c>
+      <c r="P62">
+        <v>0.1755475</v>
+      </c>
+      <c r="Q62">
+        <v>0.1755475</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3202179951994629</v>
+      </c>
+      <c r="T62">
+        <v>1.492411785054842</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.29</v>
+      </c>
+      <c r="W62">
+        <v>0.03905</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.281385281385282</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1511244863673985</v>
+      </c>
+      <c r="C63">
+        <v>1.050603578191319</v>
+      </c>
+      <c r="D63">
+        <v>2.094103578191319</v>
+      </c>
+      <c r="E63">
+        <v>1.0675</v>
+      </c>
+      <c r="F63">
+        <v>1.0675</v>
+      </c>
+      <c r="G63">
+        <v>0.024</v>
+      </c>
+      <c r="H63">
+        <v>1.75</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.305</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0.305</v>
+      </c>
+      <c r="M63">
+        <v>0.05871249999999999</v>
+      </c>
+      <c r="N63">
+        <v>0.2462875</v>
+      </c>
+      <c r="O63">
+        <v>0.07142337500000001</v>
+      </c>
+      <c r="P63">
+        <v>0.174864125</v>
+      </c>
+      <c r="Q63">
+        <v>0.174864125</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3264204778651244</v>
+      </c>
+      <c r="T63">
+        <v>1.525304700165941</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.29</v>
+      </c>
+      <c r="W63">
+        <v>0.03905</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.194805194805195</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1507317746550119</v>
+      </c>
+      <c r="C64">
+        <v>1.04045072340224</v>
+      </c>
+      <c r="D64">
+        <v>2.10145072340224</v>
+      </c>
+      <c r="E64">
+        <v>1.085</v>
+      </c>
+      <c r="F64">
+        <v>1.085</v>
+      </c>
+      <c r="G64">
+        <v>0.024</v>
+      </c>
+      <c r="H64">
+        <v>1.75</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.305</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0.305</v>
+      </c>
+      <c r="M64">
+        <v>0.059675</v>
+      </c>
+      <c r="N64">
+        <v>0.245325</v>
+      </c>
+      <c r="O64">
+        <v>0.07114425000000001</v>
+      </c>
+      <c r="P64">
+        <v>0.17418075</v>
+      </c>
+      <c r="Q64">
+        <v>0.17418075</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3329494069868734</v>
+      </c>
+      <c r="T64">
+        <v>1.559928821335519</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.29</v>
+      </c>
+      <c r="W64">
+        <v>0.03905</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.111018014243821</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1503390629426252</v>
+      </c>
+      <c r="C65">
+        <v>1.030349604926895</v>
+      </c>
+      <c r="D65">
+        <v>2.108849604926895</v>
+      </c>
+      <c r="E65">
+        <v>1.1025</v>
+      </c>
+      <c r="F65">
+        <v>1.1025</v>
+      </c>
+      <c r="G65">
+        <v>0.024</v>
+      </c>
+      <c r="H65">
+        <v>1.75</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.305</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0.305</v>
+      </c>
+      <c r="M65">
+        <v>0.0606375</v>
+      </c>
+      <c r="N65">
+        <v>0.2443625</v>
+      </c>
+      <c r="O65">
+        <v>0.070865125</v>
+      </c>
+      <c r="P65">
+        <v>0.173497375</v>
+      </c>
+      <c r="Q65">
+        <v>0.173497375</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3398312511962844</v>
+      </c>
+      <c r="T65">
+        <v>1.596424516622371</v>
+      </c>
+      <c r="U65">
+        <v>0.055</v>
+      </c>
+      <c r="V65">
+        <v>0.29</v>
+      </c>
+      <c r="W65">
+        <v>0.03905</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.029890744176458</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1499463512302386</v>
+      </c>
+      <c r="C66">
+        <v>1.020300771162673</v>
+      </c>
+      <c r="D66">
+        <v>2.116300771162673</v>
+      </c>
+      <c r="E66">
+        <v>1.12</v>
+      </c>
+      <c r="F66">
+        <v>1.12</v>
+      </c>
+      <c r="G66">
+        <v>0.024</v>
+      </c>
+      <c r="H66">
+        <v>1.75</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.305</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0.305</v>
+      </c>
+      <c r="M66">
+        <v>0.06160000000000001</v>
+      </c>
+      <c r="N66">
+        <v>0.2434</v>
+      </c>
+      <c r="O66">
+        <v>0.070586</v>
+      </c>
+      <c r="P66">
+        <v>0.172814</v>
+      </c>
+      <c r="Q66">
+        <v>0.172814</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3470954200839961</v>
+      </c>
+      <c r="T66">
+        <v>1.634947750536271</v>
+      </c>
+      <c r="U66">
+        <v>0.055</v>
+      </c>
+      <c r="V66">
+        <v>0.29</v>
+      </c>
+      <c r="W66">
+        <v>0.03905</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>4.9512987012987</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1495536395178519</v>
+      </c>
+      <c r="C67">
+        <v>1.010304778285027</v>
+      </c>
+      <c r="D67">
+        <v>2.123804778285026</v>
+      </c>
+      <c r="E67">
+        <v>1.1375</v>
+      </c>
+      <c r="F67">
+        <v>1.1375</v>
+      </c>
+      <c r="G67">
+        <v>0.024</v>
+      </c>
+      <c r="H67">
+        <v>1.75</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.305</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0.305</v>
+      </c>
+      <c r="M67">
+        <v>0.06256249999999999</v>
+      </c>
+      <c r="N67">
+        <v>0.2424375</v>
+      </c>
+      <c r="O67">
+        <v>0.070306875</v>
+      </c>
+      <c r="P67">
+        <v>0.172130625</v>
+      </c>
+      <c r="Q67">
+        <v>0.172130625</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3547746843367198</v>
+      </c>
+      <c r="T67">
+        <v>1.675672312102393</v>
+      </c>
+      <c r="U67">
+        <v>0.055</v>
+      </c>
+      <c r="V67">
+        <v>0.29</v>
+      </c>
+      <c r="W67">
+        <v>0.03905</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>4.875124875124875</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1491609278054652</v>
+      </c>
+      <c r="C68">
+        <v>1.000362190385852</v>
+      </c>
+      <c r="D68">
+        <v>2.131362190385852</v>
+      </c>
+      <c r="E68">
+        <v>1.155</v>
+      </c>
+      <c r="F68">
+        <v>1.155</v>
+      </c>
+      <c r="G68">
+        <v>0.024</v>
+      </c>
+      <c r="H68">
+        <v>1.75</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.305</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0.305</v>
+      </c>
+      <c r="M68">
+        <v>0.063525</v>
+      </c>
+      <c r="N68">
+        <v>0.241475</v>
+      </c>
+      <c r="O68">
+        <v>0.07002775000000001</v>
+      </c>
+      <c r="P68">
+        <v>0.17144725</v>
+      </c>
+      <c r="Q68">
+        <v>0.17144725</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3629056700160743</v>
+      </c>
+      <c r="T68">
+        <v>1.718792436113582</v>
+      </c>
+      <c r="U68">
+        <v>0.055</v>
+      </c>
+      <c r="V68">
+        <v>0.29</v>
+      </c>
+      <c r="W68">
+        <v>0.03905</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.801259346713892</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1487682160930786</v>
+      </c>
+      <c r="C69">
+        <v>0.9904735796148463</v>
+      </c>
+      <c r="D69">
+        <v>2.138973579614846</v>
+      </c>
+      <c r="E69">
+        <v>1.1725</v>
+      </c>
+      <c r="F69">
+        <v>1.1725</v>
+      </c>
+      <c r="G69">
+        <v>0.024</v>
+      </c>
+      <c r="H69">
+        <v>1.75</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.305</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0.305</v>
+      </c>
+      <c r="M69">
+        <v>0.0644875</v>
+      </c>
+      <c r="N69">
+        <v>0.2405125</v>
+      </c>
+      <c r="O69">
+        <v>0.06974862500000001</v>
+      </c>
+      <c r="P69">
+        <v>0.170763875</v>
+      </c>
+      <c r="Q69">
+        <v>0.170763875</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3715294427062988</v>
+      </c>
+      <c r="T69">
+        <v>1.764525900973933</v>
+      </c>
+      <c r="U69">
+        <v>0.055</v>
+      </c>
+      <c r="V69">
+        <v>0.29</v>
+      </c>
+      <c r="W69">
+        <v>0.03905</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>4.729598759449505</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1483755043806919</v>
+      </c>
+      <c r="C70">
+        <v>0.9806395263239021</v>
+      </c>
+      <c r="D70">
+        <v>2.146639526323902</v>
+      </c>
+      <c r="E70">
+        <v>1.19</v>
+      </c>
+      <c r="F70">
+        <v>1.19</v>
+      </c>
+      <c r="G70">
+        <v>0.024</v>
+      </c>
+      <c r="H70">
+        <v>1.75</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.305</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0.305</v>
+      </c>
+      <c r="M70">
+        <v>0.06545000000000001</v>
+      </c>
+      <c r="N70">
+        <v>0.23955</v>
+      </c>
+      <c r="O70">
+        <v>0.0694695</v>
+      </c>
+      <c r="P70">
+        <v>0.1700805</v>
+      </c>
+      <c r="Q70">
+        <v>0.1700805</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3806922011896623</v>
+      </c>
+      <c r="T70">
+        <v>1.813117707388056</v>
+      </c>
+      <c r="U70">
+        <v>0.055</v>
+      </c>
+      <c r="V70">
+        <v>0.29</v>
+      </c>
+      <c r="W70">
+        <v>0.03905</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>4.660045836516424</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1479827926683053</v>
+      </c>
+      <c r="C71">
+        <v>0.9708606192146161</v>
+      </c>
+      <c r="D71">
+        <v>2.154360619214616</v>
+      </c>
+      <c r="E71">
+        <v>1.2075</v>
+      </c>
+      <c r="F71">
+        <v>1.2075</v>
+      </c>
+      <c r="G71">
+        <v>0.024</v>
+      </c>
+      <c r="H71">
+        <v>1.75</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.305</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0.305</v>
+      </c>
+      <c r="M71">
+        <v>0.0664125</v>
+      </c>
+      <c r="N71">
+        <v>0.2385875</v>
+      </c>
+      <c r="O71">
+        <v>0.06919037500000001</v>
+      </c>
+      <c r="P71">
+        <v>0.169397125</v>
+      </c>
+      <c r="Q71">
+        <v>0.169397125</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.39044610538163</v>
+      </c>
+      <c r="T71">
+        <v>1.864844469054704</v>
+      </c>
+      <c r="U71">
+        <v>0.055</v>
+      </c>
+      <c r="V71">
+        <v>0.29</v>
+      </c>
+      <c r="W71">
+        <v>0.03905</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>4.592508940335028</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1475900809559186</v>
+      </c>
+      <c r="C72">
+        <v>0.9611374554889909</v>
+      </c>
+      <c r="D72">
+        <v>2.162137455488991</v>
+      </c>
+      <c r="E72">
+        <v>1.225</v>
+      </c>
+      <c r="F72">
+        <v>1.225</v>
+      </c>
+      <c r="G72">
+        <v>0.024</v>
+      </c>
+      <c r="H72">
+        <v>1.75</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.305</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0.305</v>
+      </c>
+      <c r="M72">
+        <v>0.067375</v>
+      </c>
+      <c r="N72">
+        <v>0.237625</v>
+      </c>
+      <c r="O72">
+        <v>0.06891125000000001</v>
+      </c>
+      <c r="P72">
+        <v>0.16871375</v>
+      </c>
+      <c r="Q72">
+        <v>0.16871375</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4008502698530622</v>
+      </c>
+      <c r="T72">
+        <v>1.920019681499128</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.29</v>
+      </c>
+      <c r="W72">
+        <v>0.03905</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>4.526901669758812</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.149112949243532</v>
+      </c>
+      <c r="C73">
+        <v>0.9137891866592247</v>
+      </c>
+      <c r="D73">
+        <v>2.132289186659225</v>
+      </c>
+      <c r="E73">
+        <v>1.2425</v>
+      </c>
+      <c r="F73">
+        <v>1.2425</v>
+      </c>
+      <c r="G73">
+        <v>0.024</v>
+      </c>
+      <c r="H73">
+        <v>1.75</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.305</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0.305</v>
+      </c>
+      <c r="M73">
+        <v>0.073059</v>
+      </c>
+      <c r="N73">
+        <v>0.231941</v>
+      </c>
+      <c r="O73">
+        <v>0.06726289000000001</v>
+      </c>
+      <c r="P73">
+        <v>0.16467811</v>
+      </c>
+      <c r="Q73">
+        <v>0.16467811</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.411971962908731</v>
+      </c>
+      <c r="T73">
+        <v>1.979000081008684</v>
+      </c>
+      <c r="U73">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.29</v>
+      </c>
+      <c r="W73">
+        <v>0.041748</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>4.174708112621307</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1487472175311453</v>
+      </c>
+      <c r="C74">
+        <v>0.903382097176215</v>
+      </c>
+      <c r="D74">
+        <v>2.139382097176215</v>
+      </c>
+      <c r="E74">
+        <v>1.26</v>
+      </c>
+      <c r="F74">
+        <v>1.26</v>
+      </c>
+      <c r="G74">
+        <v>0.024</v>
+      </c>
+      <c r="H74">
+        <v>1.75</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.305</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0.305</v>
+      </c>
+      <c r="M74">
+        <v>0.074088</v>
+      </c>
+      <c r="N74">
+        <v>0.230912</v>
+      </c>
+      <c r="O74">
+        <v>0.06696448000000001</v>
+      </c>
+      <c r="P74">
+        <v>0.16394752</v>
+      </c>
+      <c r="Q74">
+        <v>0.16394752</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4238880626112333</v>
+      </c>
+      <c r="T74">
+        <v>2.042193366197494</v>
+      </c>
+      <c r="U74">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.29</v>
+      </c>
+      <c r="W74">
+        <v>0.041748</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.116726055501566</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1483814858187587</v>
+      </c>
+      <c r="C75">
+        <v>0.8930223533244459</v>
+      </c>
+      <c r="D75">
+        <v>2.146522353324446</v>
+      </c>
+      <c r="E75">
+        <v>1.2775</v>
+      </c>
+      <c r="F75">
+        <v>1.2775</v>
+      </c>
+      <c r="G75">
+        <v>0.024</v>
+      </c>
+      <c r="H75">
+        <v>1.75</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.305</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0.305</v>
+      </c>
+      <c r="M75">
+        <v>0.075117</v>
+      </c>
+      <c r="N75">
+        <v>0.229883</v>
+      </c>
+      <c r="O75">
+        <v>0.06666607000000001</v>
+      </c>
+      <c r="P75">
+        <v>0.16321693</v>
+      </c>
+      <c r="Q75">
+        <v>0.16321693</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4366868363657728</v>
+      </c>
+      <c r="T75">
+        <v>2.110067635474365</v>
+      </c>
+      <c r="U75">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.29</v>
+      </c>
+      <c r="W75">
+        <v>0.041748</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.060332547891955</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.148015754106372</v>
+      </c>
+      <c r="C76">
+        <v>0.8827104307440545</v>
+      </c>
+      <c r="D76">
+        <v>2.153710430744054</v>
+      </c>
+      <c r="E76">
+        <v>1.295</v>
+      </c>
+      <c r="F76">
+        <v>1.295</v>
+      </c>
+      <c r="G76">
+        <v>0.024</v>
+      </c>
+      <c r="H76">
+        <v>1.75</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.305</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0.305</v>
+      </c>
+      <c r="M76">
+        <v>0.07614600000000001</v>
+      </c>
+      <c r="N76">
+        <v>0.228854</v>
+      </c>
+      <c r="O76">
+        <v>0.06636766000000001</v>
+      </c>
+      <c r="P76">
+        <v>0.16248634</v>
+      </c>
+      <c r="Q76">
+        <v>0.16248634</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4504701311783539</v>
+      </c>
+      <c r="T76">
+        <v>2.183163002387918</v>
+      </c>
+      <c r="U76">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.29</v>
+      </c>
+      <c r="W76">
+        <v>0.041748</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.005463189136659</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1498865223939854</v>
+      </c>
+      <c r="C77">
+        <v>0.8289405657081481</v>
+      </c>
+      <c r="D77">
+        <v>2.117440565708148</v>
+      </c>
+      <c r="E77">
+        <v>1.3125</v>
+      </c>
+      <c r="F77">
+        <v>1.3125</v>
+      </c>
+      <c r="G77">
+        <v>0.024</v>
+      </c>
+      <c r="H77">
+        <v>1.75</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.305</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0.305</v>
+      </c>
+      <c r="M77">
+        <v>0.0826875</v>
+      </c>
+      <c r="N77">
+        <v>0.2223125</v>
+      </c>
+      <c r="O77">
+        <v>0.064470625</v>
+      </c>
+      <c r="P77">
+        <v>0.157841875</v>
+      </c>
+      <c r="Q77">
+        <v>0.157841875</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4653560895759414</v>
+      </c>
+      <c r="T77">
+        <v>2.262105998654555</v>
+      </c>
+      <c r="U77">
+        <v>0.063</v>
+      </c>
+      <c r="V77">
+        <v>0.29</v>
+      </c>
+      <c r="W77">
+        <v>0.04473</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>3.688586545729403</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1495506106815987</v>
+      </c>
+      <c r="C78">
+        <v>0.8178628606456342</v>
+      </c>
+      <c r="D78">
+        <v>2.123862860645634</v>
+      </c>
+      <c r="E78">
+        <v>1.33</v>
+      </c>
+      <c r="F78">
+        <v>1.33</v>
+      </c>
+      <c r="G78">
+        <v>0.024</v>
+      </c>
+      <c r="H78">
+        <v>1.75</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.305</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0.305</v>
+      </c>
+      <c r="M78">
+        <v>0.08379</v>
+      </c>
+      <c r="N78">
+        <v>0.22121</v>
+      </c>
+      <c r="O78">
+        <v>0.06415090000000001</v>
+      </c>
+      <c r="P78">
+        <v>0.1570591</v>
+      </c>
+      <c r="Q78">
+        <v>0.1570591</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4814825445066613</v>
+      </c>
+      <c r="T78">
+        <v>2.347627577943412</v>
+      </c>
+      <c r="U78">
+        <v>0.063</v>
+      </c>
+      <c r="V78">
+        <v>0.29</v>
+      </c>
+      <c r="W78">
+        <v>0.04473</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>3.640052512232963</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1492146989692121</v>
+      </c>
+      <c r="C79">
+        <v>0.806824232338482</v>
+      </c>
+      <c r="D79">
+        <v>2.130324232338482</v>
+      </c>
+      <c r="E79">
+        <v>1.3475</v>
+      </c>
+      <c r="F79">
+        <v>1.3475</v>
+      </c>
+      <c r="G79">
+        <v>0.024</v>
+      </c>
+      <c r="H79">
+        <v>1.75</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.305</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0.305</v>
+      </c>
+      <c r="M79">
+        <v>0.08489250000000001</v>
+      </c>
+      <c r="N79">
+        <v>0.2201075</v>
+      </c>
+      <c r="O79">
+        <v>0.063831175</v>
+      </c>
+      <c r="P79">
+        <v>0.156276325</v>
+      </c>
+      <c r="Q79">
+        <v>0.156276325</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4990112998661394</v>
+      </c>
+      <c r="T79">
+        <v>2.440585816300866</v>
+      </c>
+      <c r="U79">
+        <v>0.063</v>
+      </c>
+      <c r="V79">
+        <v>0.29</v>
+      </c>
+      <c r="W79">
+        <v>0.04473</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>3.592779102983184</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1488787872568254</v>
+      </c>
+      <c r="C80">
+        <v>0.7958250385215482</v>
+      </c>
+      <c r="D80">
+        <v>2.136825038521548</v>
+      </c>
+      <c r="E80">
+        <v>1.365</v>
+      </c>
+      <c r="F80">
+        <v>1.365</v>
+      </c>
+      <c r="G80">
+        <v>0.024</v>
+      </c>
+      <c r="H80">
+        <v>1.75</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.305</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0.305</v>
+      </c>
+      <c r="M80">
+        <v>0.085995</v>
+      </c>
+      <c r="N80">
+        <v>0.219005</v>
+      </c>
+      <c r="O80">
+        <v>0.06351145000000001</v>
+      </c>
+      <c r="P80">
+        <v>0.15549355</v>
+      </c>
+      <c r="Q80">
+        <v>0.15549355</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5181335784401155</v>
+      </c>
+      <c r="T80">
+        <v>2.541994803599906</v>
+      </c>
+      <c r="U80">
+        <v>0.063</v>
+      </c>
+      <c r="V80">
+        <v>0.29</v>
+      </c>
+      <c r="W80">
+        <v>0.04473</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>3.546717832432118</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1485428755444388</v>
+      </c>
+      <c r="C81">
+        <v>0.7848656413096513</v>
+      </c>
+      <c r="D81">
+        <v>2.143365641309651</v>
+      </c>
+      <c r="E81">
+        <v>1.3825</v>
+      </c>
+      <c r="F81">
+        <v>1.3825</v>
+      </c>
+      <c r="G81">
+        <v>0.024</v>
+      </c>
+      <c r="H81">
+        <v>1.75</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.305</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0.305</v>
+      </c>
+      <c r="M81">
+        <v>0.08709750000000001</v>
+      </c>
+      <c r="N81">
+        <v>0.2179025</v>
+      </c>
+      <c r="O81">
+        <v>0.063191725</v>
+      </c>
+      <c r="P81">
+        <v>0.154710775</v>
+      </c>
+      <c r="Q81">
+        <v>0.154710775</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5390770264020894</v>
+      </c>
+      <c r="T81">
+        <v>2.65306178968933</v>
+      </c>
+      <c r="U81">
+        <v>0.063</v>
+      </c>
+      <c r="V81">
+        <v>0.29</v>
+      </c>
+      <c r="W81">
+        <v>0.04473</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>3.501822669996268</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1522397638320521</v>
+      </c>
+      <c r="C82">
+        <v>0.6975155017486976</v>
+      </c>
+      <c r="D82">
+        <v>2.073515501748698</v>
+      </c>
+      <c r="E82">
+        <v>1.4</v>
+      </c>
+      <c r="F82">
+        <v>1.4</v>
+      </c>
+      <c r="G82">
+        <v>0.024</v>
+      </c>
+      <c r="H82">
+        <v>1.75</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.305</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0.305</v>
+      </c>
+      <c r="M82">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="N82">
+        <v>0.20686</v>
+      </c>
+      <c r="O82">
+        <v>0.05998940000000001</v>
+      </c>
+      <c r="P82">
+        <v>0.1468706</v>
+      </c>
+      <c r="Q82">
+        <v>0.1468706</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5621148191602605</v>
+      </c>
+      <c r="T82">
+        <v>2.775235474387697</v>
+      </c>
+      <c r="U82">
+        <v>0.0701</v>
+      </c>
+      <c r="V82">
+        <v>0.29</v>
+      </c>
+      <c r="W82">
+        <v>0.049771</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>3.107805176278785</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1519542621196655</v>
+      </c>
+      <c r="C83">
+        <v>0.6852472289087705</v>
+      </c>
+      <c r="D83">
+        <v>2.078747228908771</v>
+      </c>
+      <c r="E83">
+        <v>1.4175</v>
+      </c>
+      <c r="F83">
+        <v>1.4175</v>
+      </c>
+      <c r="G83">
+        <v>0.024</v>
+      </c>
+      <c r="H83">
+        <v>1.75</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.305</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0.305</v>
+      </c>
+      <c r="M83">
+        <v>0.09936674999999999</v>
+      </c>
+      <c r="N83">
+        <v>0.20563325</v>
+      </c>
+      <c r="O83">
+        <v>0.05963364250000001</v>
+      </c>
+      <c r="P83">
+        <v>0.1459996075</v>
+      </c>
+      <c r="Q83">
+        <v>0.1459996075</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5875776427350814</v>
+      </c>
+      <c r="T83">
+        <v>2.910269546949051</v>
+      </c>
+      <c r="U83">
+        <v>0.0701</v>
+      </c>
+      <c r="V83">
+        <v>0.29</v>
+      </c>
+      <c r="W83">
+        <v>0.049771</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>3.069437211139541</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1516687604072788</v>
+      </c>
+      <c r="C84">
+        <v>0.6730054233935063</v>
+      </c>
+      <c r="D84">
+        <v>2.084005423393506</v>
+      </c>
+      <c r="E84">
+        <v>1.435</v>
+      </c>
+      <c r="F84">
+        <v>1.435</v>
+      </c>
+      <c r="G84">
+        <v>0.024</v>
+      </c>
+      <c r="H84">
+        <v>1.75</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.305</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0.305</v>
+      </c>
+      <c r="M84">
+        <v>0.1005935</v>
+      </c>
+      <c r="N84">
+        <v>0.2044065</v>
+      </c>
+      <c r="O84">
+        <v>0.059277885</v>
+      </c>
+      <c r="P84">
+        <v>0.145128615</v>
+      </c>
+      <c r="Q84">
+        <v>0.145128615</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6158696689293268</v>
+      </c>
+      <c r="T84">
+        <v>3.060307405350555</v>
+      </c>
+      <c r="U84">
+        <v>0.0701</v>
+      </c>
+      <c r="V84">
+        <v>0.29</v>
+      </c>
+      <c r="W84">
+        <v>0.049771</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>3.032005050028083</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1639353486948921</v>
+      </c>
+      <c r="C85">
+        <v>0.4512175320459439</v>
+      </c>
+      <c r="D85">
+        <v>1.879717532045944</v>
+      </c>
+      <c r="E85">
+        <v>1.4525</v>
+      </c>
+      <c r="F85">
+        <v>1.4525</v>
+      </c>
+      <c r="G85">
+        <v>0.024</v>
+      </c>
+      <c r="H85">
+        <v>1.75</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.305</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0.305</v>
+      </c>
+      <c r="M85">
+        <v>0.1327585</v>
+      </c>
+      <c r="N85">
+        <v>0.1722415</v>
+      </c>
+      <c r="O85">
+        <v>0.049950035</v>
+      </c>
+      <c r="P85">
+        <v>0.122291465</v>
+      </c>
+      <c r="Q85">
+        <v>0.122291465</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6474901687934833</v>
+      </c>
+      <c r="T85">
+        <v>3.227996776505176</v>
+      </c>
+      <c r="U85">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V85">
+        <v>0.29</v>
+      </c>
+      <c r="W85">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>2.297404685952311</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1638010769825055</v>
+      </c>
+      <c r="C86">
+        <v>0.4357366577840871</v>
+      </c>
+      <c r="D86">
+        <v>1.881736657784087</v>
+      </c>
+      <c r="E86">
+        <v>1.47</v>
+      </c>
+      <c r="F86">
+        <v>1.47</v>
+      </c>
+      <c r="G86">
+        <v>0.024</v>
+      </c>
+      <c r="H86">
+        <v>1.75</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.305</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0.305</v>
+      </c>
+      <c r="M86">
+        <v>0.134358</v>
+      </c>
+      <c r="N86">
+        <v>0.170642</v>
+      </c>
+      <c r="O86">
+        <v>0.04948618</v>
+      </c>
+      <c r="P86">
+        <v>0.12115582</v>
+      </c>
+      <c r="Q86">
+        <v>0.12115582</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.683063231140659</v>
+      </c>
+      <c r="T86">
+        <v>3.416647319054124</v>
+      </c>
+      <c r="U86">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V86">
+        <v>0.29</v>
+      </c>
+      <c r="W86">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>2.270054630167165</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1636668052701188</v>
+      </c>
+      <c r="C87">
+        <v>0.420260125932846</v>
+      </c>
+      <c r="D87">
+        <v>1.883760125932846</v>
+      </c>
+      <c r="E87">
+        <v>1.4875</v>
+      </c>
+      <c r="F87">
+        <v>1.4875</v>
+      </c>
+      <c r="G87">
+        <v>0.024</v>
+      </c>
+      <c r="H87">
+        <v>1.75</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.305</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0.305</v>
+      </c>
+      <c r="M87">
+        <v>0.1359575</v>
+      </c>
+      <c r="N87">
+        <v>0.1690425</v>
+      </c>
+      <c r="O87">
+        <v>0.049022325</v>
+      </c>
+      <c r="P87">
+        <v>0.120020175</v>
+      </c>
+      <c r="Q87">
+        <v>0.120020175</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7233793684674588</v>
+      </c>
+      <c r="T87">
+        <v>3.630451267276267</v>
+      </c>
+      <c r="U87">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V87">
+        <v>0.29</v>
+      </c>
+      <c r="W87">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>2.243348105106375</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1635325335577322</v>
+      </c>
+      <c r="C88">
+        <v>0.4047879505157377</v>
+      </c>
+      <c r="D88">
+        <v>1.885787950515738</v>
+      </c>
+      <c r="E88">
+        <v>1.505</v>
+      </c>
+      <c r="F88">
+        <v>1.505</v>
+      </c>
+      <c r="G88">
+        <v>0.024</v>
+      </c>
+      <c r="H88">
+        <v>1.75</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.305</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0.305</v>
+      </c>
+      <c r="M88">
+        <v>0.137557</v>
+      </c>
+      <c r="N88">
+        <v>0.167443</v>
+      </c>
+      <c r="O88">
+        <v>0.04855847</v>
+      </c>
+      <c r="P88">
+        <v>0.11888453</v>
+      </c>
+      <c r="Q88">
+        <v>0.11888453</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7694549539838011</v>
+      </c>
+      <c r="T88">
+        <v>3.874798636673001</v>
+      </c>
+      <c r="U88">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V88">
+        <v>0.29</v>
+      </c>
+      <c r="W88">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>2.217262662023742</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1633982618453455</v>
+      </c>
+      <c r="C89">
+        <v>0.389320145616727</v>
+      </c>
+      <c r="D89">
+        <v>1.887820145616727</v>
+      </c>
+      <c r="E89">
+        <v>1.5225</v>
+      </c>
+      <c r="F89">
+        <v>1.5225</v>
+      </c>
+      <c r="G89">
+        <v>0.024</v>
+      </c>
+      <c r="H89">
+        <v>1.75</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.305</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0.305</v>
+      </c>
+      <c r="M89">
+        <v>0.1391565</v>
+      </c>
+      <c r="N89">
+        <v>0.1658435</v>
+      </c>
+      <c r="O89">
+        <v>0.048094615</v>
+      </c>
+      <c r="P89">
+        <v>0.117748885</v>
+      </c>
+      <c r="Q89">
+        <v>0.117748885</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8226190911180422</v>
+      </c>
+      <c r="T89">
+        <v>4.156737909053848</v>
+      </c>
+      <c r="U89">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V89">
+        <v>0.29</v>
+      </c>
+      <c r="W89">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>2.191776884299331</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1632639901329588</v>
+      </c>
+      <c r="C90">
+        <v>0.3738567253805545</v>
+      </c>
+      <c r="D90">
+        <v>1.889856725380554</v>
+      </c>
+      <c r="E90">
+        <v>1.54</v>
+      </c>
+      <c r="F90">
+        <v>1.54</v>
+      </c>
+      <c r="G90">
+        <v>0.024</v>
+      </c>
+      <c r="H90">
+        <v>1.75</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.305</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0.305</v>
+      </c>
+      <c r="M90">
+        <v>0.140756</v>
+      </c>
+      <c r="N90">
+        <v>0.164244</v>
+      </c>
+      <c r="O90">
+        <v>0.04763076</v>
+      </c>
+      <c r="P90">
+        <v>0.11661324</v>
+      </c>
+      <c r="Q90">
+        <v>0.11661324</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.884643917774657</v>
+      </c>
+      <c r="T90">
+        <v>4.485667060164837</v>
+      </c>
+      <c r="U90">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V90">
+        <v>0.29</v>
+      </c>
+      <c r="W90">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>2.16687032879593</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1631297184205722</v>
+      </c>
+      <c r="C91">
+        <v>0.3583977040130637</v>
+      </c>
+      <c r="D91">
+        <v>1.891897704013064</v>
+      </c>
+      <c r="E91">
+        <v>1.5575</v>
+      </c>
+      <c r="F91">
+        <v>1.5575</v>
+      </c>
+      <c r="G91">
+        <v>0.024</v>
+      </c>
+      <c r="H91">
+        <v>1.75</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.305</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0.305</v>
+      </c>
+      <c r="M91">
+        <v>0.1423555</v>
+      </c>
+      <c r="N91">
+        <v>0.1626445</v>
+      </c>
+      <c r="O91">
+        <v>0.047166905</v>
+      </c>
+      <c r="P91">
+        <v>0.115477595</v>
+      </c>
+      <c r="Q91">
+        <v>0.115477595</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9579459856415655</v>
+      </c>
+      <c r="T91">
+        <v>4.874401511477823</v>
+      </c>
+      <c r="U91">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V91">
+        <v>0.29</v>
+      </c>
+      <c r="W91">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>2.142523471169009</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1629954467081855</v>
+      </c>
+      <c r="C92">
+        <v>0.3429430957815327</v>
+      </c>
+      <c r="D92">
+        <v>1.893943095781533</v>
+      </c>
+      <c r="E92">
+        <v>1.575</v>
+      </c>
+      <c r="F92">
+        <v>1.575</v>
+      </c>
+      <c r="G92">
+        <v>0.024</v>
+      </c>
+      <c r="H92">
+        <v>1.75</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.305</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0.305</v>
+      </c>
+      <c r="M92">
+        <v>0.143955</v>
+      </c>
+      <c r="N92">
+        <v>0.161045</v>
+      </c>
+      <c r="O92">
+        <v>0.04670305</v>
+      </c>
+      <c r="P92">
+        <v>0.11434195</v>
+      </c>
+      <c r="Q92">
+        <v>0.11434195</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.045908467081855</v>
+      </c>
+      <c r="T92">
+        <v>5.340882853053407</v>
+      </c>
+      <c r="U92">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V92">
+        <v>0.29</v>
+      </c>
+      <c r="W92">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>2.118717654822688</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1628611749957989</v>
+      </c>
+      <c r="C93">
+        <v>0.3274929150150034</v>
+      </c>
+      <c r="D93">
+        <v>1.895992915015003</v>
+      </c>
+      <c r="E93">
+        <v>1.5925</v>
+      </c>
+      <c r="F93">
+        <v>1.5925</v>
+      </c>
+      <c r="G93">
+        <v>0.024</v>
+      </c>
+      <c r="H93">
+        <v>1.75</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.305</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0.305</v>
+      </c>
+      <c r="M93">
+        <v>0.1455545</v>
+      </c>
+      <c r="N93">
+        <v>0.1594455</v>
+      </c>
+      <c r="O93">
+        <v>0.046239195</v>
+      </c>
+      <c r="P93">
+        <v>0.113206305</v>
+      </c>
+      <c r="Q93">
+        <v>0.113206305</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.153418166619988</v>
+      </c>
+      <c r="T93">
+        <v>5.911026714979123</v>
+      </c>
+      <c r="U93">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V93">
+        <v>0.29</v>
+      </c>
+      <c r="W93">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>2.095435043231229</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1627269032834122</v>
+      </c>
+      <c r="C94">
+        <v>0.3120471761046224</v>
+      </c>
+      <c r="D94">
+        <v>1.898047176104622</v>
+      </c>
+      <c r="E94">
+        <v>1.61</v>
+      </c>
+      <c r="F94">
+        <v>1.61</v>
+      </c>
+      <c r="G94">
+        <v>0.024</v>
+      </c>
+      <c r="H94">
+        <v>1.75</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.305</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0.305</v>
+      </c>
+      <c r="M94">
+        <v>0.147154</v>
+      </c>
+      <c r="N94">
+        <v>0.157846</v>
+      </c>
+      <c r="O94">
+        <v>0.04577533999999999</v>
+      </c>
+      <c r="P94">
+        <v>0.11207066</v>
+      </c>
+      <c r="Q94">
+        <v>0.11207066</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.287805291042653</v>
+      </c>
+      <c r="T94">
+        <v>6.623706542386265</v>
+      </c>
+      <c r="U94">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V94">
+        <v>0.29</v>
+      </c>
+      <c r="W94">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>2.07265857537002</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1625926315710255</v>
+      </c>
+      <c r="C95">
+        <v>0.2966058935039697</v>
+      </c>
+      <c r="D95">
+        <v>1.90010589350397</v>
+      </c>
+      <c r="E95">
+        <v>1.6275</v>
+      </c>
+      <c r="F95">
+        <v>1.6275</v>
+      </c>
+      <c r="G95">
+        <v>0.024</v>
+      </c>
+      <c r="H95">
+        <v>1.75</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.305</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0.305</v>
+      </c>
+      <c r="M95">
+        <v>0.1487535</v>
+      </c>
+      <c r="N95">
+        <v>0.1562465</v>
+      </c>
+      <c r="O95">
+        <v>0.04531148499999999</v>
+      </c>
+      <c r="P95">
+        <v>0.110935015</v>
+      </c>
+      <c r="Q95">
+        <v>0.110935015</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.460588736728937</v>
+      </c>
+      <c r="T95">
+        <v>7.540009177624019</v>
+      </c>
+      <c r="U95">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.29</v>
+      </c>
+      <c r="W95">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>2.050371924021955</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1624583598586389</v>
+      </c>
+      <c r="C96">
+        <v>0.2811690817294028</v>
+      </c>
+      <c r="D96">
+        <v>1.902169081729403</v>
+      </c>
+      <c r="E96">
+        <v>1.645</v>
+      </c>
+      <c r="F96">
+        <v>1.645</v>
+      </c>
+      <c r="G96">
+        <v>0.024</v>
+      </c>
+      <c r="H96">
+        <v>1.75</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.305</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0.305</v>
+      </c>
+      <c r="M96">
+        <v>0.150353</v>
+      </c>
+      <c r="N96">
+        <v>0.154647</v>
+      </c>
+      <c r="O96">
+        <v>0.04484763</v>
+      </c>
+      <c r="P96">
+        <v>0.10979937</v>
+      </c>
+      <c r="Q96">
+        <v>0.10979937</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.69096666431065</v>
+      </c>
+      <c r="T96">
+        <v>8.761746024607694</v>
+      </c>
+      <c r="U96">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.29</v>
+      </c>
+      <c r="W96">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.028559456745126</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1623240881462523</v>
+      </c>
+      <c r="C97">
+        <v>0.2657367553603982</v>
+      </c>
+      <c r="D97">
+        <v>1.904236755360398</v>
+      </c>
+      <c r="E97">
+        <v>1.6625</v>
+      </c>
+      <c r="F97">
+        <v>1.6625</v>
+      </c>
+      <c r="G97">
+        <v>0.024</v>
+      </c>
+      <c r="H97">
+        <v>1.75</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.305</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0.305</v>
+      </c>
+      <c r="M97">
+        <v>0.1519525</v>
+      </c>
+      <c r="N97">
+        <v>0.1530475</v>
+      </c>
+      <c r="O97">
+        <v>0.044383775</v>
+      </c>
+      <c r="P97">
+        <v>0.108663725</v>
+      </c>
+      <c r="Q97">
+        <v>0.108663725</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.013495762925048</v>
+      </c>
+      <c r="T97">
+        <v>10.47217761038484</v>
+      </c>
+      <c r="U97">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.29</v>
+      </c>
+      <c r="W97">
+        <v>0.06489400000000001</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.007206199305704</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1765715764338656</v>
+      </c>
+      <c r="C98">
+        <v>0.0513123129529065</v>
+      </c>
+      <c r="D98">
+        <v>1.707312312952906</v>
+      </c>
+      <c r="E98">
+        <v>1.68</v>
+      </c>
+      <c r="F98">
+        <v>1.68</v>
+      </c>
+      <c r="G98">
+        <v>0.024</v>
+      </c>
+      <c r="H98">
+        <v>1.75</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.305</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0.305</v>
+      </c>
+      <c r="M98">
+        <v>0.189</v>
+      </c>
+      <c r="N98">
+        <v>0.116</v>
+      </c>
+      <c r="O98">
+        <v>0.03364</v>
+      </c>
+      <c r="P98">
+        <v>0.08235999999999999</v>
+      </c>
+      <c r="Q98">
+        <v>0.08235999999999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.497289410846638</v>
+      </c>
+      <c r="T98">
+        <v>13.03782498905053</v>
+      </c>
+      <c r="U98">
+        <v>0.1125</v>
+      </c>
+      <c r="V98">
+        <v>0.29</v>
+      </c>
+      <c r="W98">
+        <v>0.079875</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>1.613756613756614</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1765871147214789</v>
+      </c>
+      <c r="C99">
+        <v>0.03361977891357992</v>
+      </c>
+      <c r="D99">
+        <v>1.70711977891358</v>
+      </c>
+      <c r="E99">
+        <v>1.6975</v>
+      </c>
+      <c r="F99">
+        <v>1.6975</v>
+      </c>
+      <c r="G99">
+        <v>0.024</v>
+      </c>
+      <c r="H99">
+        <v>1.75</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.305</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0.305</v>
+      </c>
+      <c r="M99">
+        <v>0.19096875</v>
+      </c>
+      <c r="N99">
+        <v>0.11403125</v>
+      </c>
+      <c r="O99">
+        <v>0.0330690625</v>
+      </c>
+      <c r="P99">
+        <v>0.0809621875</v>
+      </c>
+      <c r="Q99">
+        <v>0.0809621875</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.303612157382629</v>
+      </c>
+      <c r="T99">
+        <v>17.31390395349337</v>
+      </c>
+      <c r="U99">
+        <v>0.1125</v>
+      </c>
+      <c r="V99">
+        <v>0.29</v>
+      </c>
+      <c r="W99">
+        <v>0.079875</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>1.597119947635412</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1766026530090923</v>
+      </c>
+      <c r="C100">
+        <v>0.01592728829358103</v>
+      </c>
+      <c r="D100">
+        <v>1.706927288293581</v>
+      </c>
+      <c r="E100">
+        <v>1.715</v>
+      </c>
+      <c r="F100">
+        <v>1.715</v>
+      </c>
+      <c r="G100">
+        <v>0.024</v>
+      </c>
+      <c r="H100">
+        <v>1.75</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.305</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0.305</v>
+      </c>
+      <c r="M100">
+        <v>0.1929375</v>
+      </c>
+      <c r="N100">
+        <v>0.1120625</v>
+      </c>
+      <c r="O100">
+        <v>0.03249812500000001</v>
+      </c>
+      <c r="P100">
+        <v>0.07956437499999999</v>
+      </c>
+      <c r="Q100">
+        <v>0.07956437499999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.916257650454612</v>
+      </c>
+      <c r="T100">
+        <v>25.86606188237906</v>
+      </c>
+      <c r="U100">
+        <v>0.1125</v>
+      </c>
+      <c r="V100">
+        <v>0.29</v>
+      </c>
+      <c r="W100">
+        <v>0.079875</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>1.580822805312601</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1766181912967056</v>
+      </c>
+      <c r="C101">
+        <v>-0.001765158921775312</v>
+      </c>
+      <c r="D101">
+        <v>1.706734841078225</v>
+      </c>
+      <c r="E101">
+        <v>1.7325</v>
+      </c>
+      <c r="F101">
+        <v>1.7325</v>
+      </c>
+      <c r="G101">
+        <v>0.024</v>
+      </c>
+      <c r="H101">
+        <v>1.75</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.305</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0.305</v>
+      </c>
+      <c r="M101">
+        <v>0.19490625</v>
+      </c>
+      <c r="N101">
+        <v>0.11009375</v>
+      </c>
+      <c r="O101">
+        <v>0.0319271875</v>
+      </c>
+      <c r="P101">
+        <v>0.07816656249999998</v>
+      </c>
+      <c r="Q101">
+        <v>0.07816656249999998</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.754194129670557</v>
+      </c>
+      <c r="T101">
+        <v>51.52253566903614</v>
+      </c>
+      <c r="U101">
+        <v>0.1125</v>
+      </c>
+      <c r="V101">
+        <v>0.29</v>
+      </c>
+      <c r="W101">
+        <v>0.079875</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>1.564854898188231</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
